--- a/assets/budget-template.xlsx
+++ b/assets/budget-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/taulo/GolandProjects/budgetpipe/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F08A1D55-CED7-BA49-9C4C-33F9DF37122C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29BD43A-C337-EE4C-AF1F-EA15A41F4A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="53">
   <si>
     <t>REVENUE</t>
   </si>
@@ -199,9 +199,6 @@
   </si>
   <si>
     <t xml:space="preserve"> x</t>
-  </si>
-  <si>
-    <t>BUDGET TEMPLATE</t>
   </si>
 </sst>
 </file>
@@ -592,16 +589,6 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -619,6 +606,315 @@
       </font>
       <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -664,26 +960,6 @@
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -694,412 +970,133 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -3989,29 +3986,29 @@
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{992450C3-516C-E54A-8E9D-60C940989794}" name="tblInvestment11" displayName="tblInvestment11" ref="B35:R37" totalsRowCount="1" headerRowDxfId="36" dataDxfId="35" totalsRowDxfId="34">
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{294014AF-D891-F449-B566-7F4086B30F5D}" name="INVESTMENT" totalsRowLabel="Total" dataDxfId="33" totalsRowDxfId="32"/>
-    <tableColumn id="2" xr3:uid="{15C43410-3504-934F-9BE6-940C4BC3EB1C}" name="JAN" dataDxfId="31" totalsRowDxfId="30" dataCellStyle="Currency"/>
-    <tableColumn id="3" xr3:uid="{313B1E83-6D0C-3947-AB16-91A5B56D7B46}" name="FEB" dataDxfId="29" totalsRowDxfId="28" dataCellStyle="Currency"/>
-    <tableColumn id="4" xr3:uid="{9C5E5D1F-F6CE-2143-99A3-AD994D06E5AF}" name="MAR" dataDxfId="27" totalsRowDxfId="26" dataCellStyle="Currency"/>
-    <tableColumn id="5" xr3:uid="{C3E012AE-4AAD-2146-AF94-58319121E8DD}" name="APR" dataDxfId="25" totalsRowDxfId="24" dataCellStyle="Currency"/>
-    <tableColumn id="6" xr3:uid="{577F144F-51EC-AB4B-AF91-E945C4A1B2BC}" name="MAY" dataDxfId="23" totalsRowDxfId="22" dataCellStyle="Currency"/>
-    <tableColumn id="7" xr3:uid="{DCDB89FE-34A0-4D4E-9201-C3623E2F8896}" name="JUN" dataDxfId="21" totalsRowDxfId="20" dataCellStyle="Currency"/>
-    <tableColumn id="8" xr3:uid="{2A44951E-CCCB-0447-91FA-68374BB208D0}" name="JUL" dataDxfId="19" totalsRowDxfId="18" dataCellStyle="Currency"/>
-    <tableColumn id="9" xr3:uid="{694F199B-9ABA-D54F-95D4-E62D55AE340D}" name="AUG" dataDxfId="17" totalsRowDxfId="16" dataCellStyle="Currency"/>
-    <tableColumn id="10" xr3:uid="{73668DD0-3192-F74F-A607-7282D6844B79}" name="SEP" totalsRowFunction="sum" dataDxfId="15" totalsRowDxfId="14" dataCellStyle="Currency"/>
-    <tableColumn id="11" xr3:uid="{D1F09B50-63EF-954F-A630-252B118F69BD}" name="OCT" totalsRowFunction="sum" dataDxfId="13" totalsRowDxfId="12" dataCellStyle="Currency"/>
-    <tableColumn id="12" xr3:uid="{32F0E92C-55F7-984F-9A71-48FE200865C7}" name="NOV" totalsRowFunction="sum" dataDxfId="11" totalsRowDxfId="10" dataCellStyle="Currency"/>
-    <tableColumn id="13" xr3:uid="{41E80EA4-43CB-B740-99FD-F01662477345}" name="DEC" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="8" dataCellStyle="Currency"/>
-    <tableColumn id="14" xr3:uid="{3440B9C2-E91C-414C-96C9-BDFF292029FB}" name="TOTAL" totalsRowFunction="sum" dataDxfId="7" totalsRowDxfId="6" dataCellStyle="Currency">
+    <tableColumn id="1" xr3:uid="{294014AF-D891-F449-B566-7F4086B30F5D}" name="INVESTMENT" totalsRowLabel="Total" dataDxfId="33" totalsRowDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{15C43410-3504-934F-9BE6-940C4BC3EB1C}" name="JAN" totalsRowFunction="sum" dataDxfId="32" totalsRowDxfId="15" dataCellStyle="Currency"/>
+    <tableColumn id="3" xr3:uid="{313B1E83-6D0C-3947-AB16-91A5B56D7B46}" name="FEB" totalsRowFunction="sum" dataDxfId="31" totalsRowDxfId="14" dataCellStyle="Currency"/>
+    <tableColumn id="4" xr3:uid="{9C5E5D1F-F6CE-2143-99A3-AD994D06E5AF}" name="MAR" totalsRowFunction="sum" dataDxfId="30" totalsRowDxfId="13" dataCellStyle="Currency"/>
+    <tableColumn id="5" xr3:uid="{C3E012AE-4AAD-2146-AF94-58319121E8DD}" name="APR" totalsRowFunction="sum" dataDxfId="29" totalsRowDxfId="12" dataCellStyle="Currency"/>
+    <tableColumn id="6" xr3:uid="{577F144F-51EC-AB4B-AF91-E945C4A1B2BC}" name="MAY" totalsRowFunction="sum" dataDxfId="28" totalsRowDxfId="11" dataCellStyle="Currency"/>
+    <tableColumn id="7" xr3:uid="{DCDB89FE-34A0-4D4E-9201-C3623E2F8896}" name="JUN" totalsRowFunction="sum" dataDxfId="27" totalsRowDxfId="10" dataCellStyle="Currency"/>
+    <tableColumn id="8" xr3:uid="{2A44951E-CCCB-0447-91FA-68374BB208D0}" name="JUL" totalsRowFunction="sum" dataDxfId="26" totalsRowDxfId="9" dataCellStyle="Currency"/>
+    <tableColumn id="9" xr3:uid="{694F199B-9ABA-D54F-95D4-E62D55AE340D}" name="AUG" totalsRowFunction="sum" dataDxfId="25" totalsRowDxfId="8" dataCellStyle="Currency"/>
+    <tableColumn id="10" xr3:uid="{73668DD0-3192-F74F-A607-7282D6844B79}" name="SEP" totalsRowFunction="sum" dataDxfId="24" totalsRowDxfId="7" dataCellStyle="Currency"/>
+    <tableColumn id="11" xr3:uid="{D1F09B50-63EF-954F-A630-252B118F69BD}" name="OCT" totalsRowFunction="sum" dataDxfId="23" totalsRowDxfId="6" dataCellStyle="Currency"/>
+    <tableColumn id="12" xr3:uid="{32F0E92C-55F7-984F-9A71-48FE200865C7}" name="NOV" totalsRowFunction="sum" dataDxfId="22" totalsRowDxfId="5" dataCellStyle="Currency"/>
+    <tableColumn id="13" xr3:uid="{41E80EA4-43CB-B740-99FD-F01662477345}" name="DEC" totalsRowFunction="sum" dataDxfId="21" totalsRowDxfId="4" dataCellStyle="Currency"/>
+    <tableColumn id="14" xr3:uid="{3440B9C2-E91C-414C-96C9-BDFF292029FB}" name="TOTAL" totalsRowFunction="sum" dataDxfId="20" totalsRowDxfId="3" dataCellStyle="Currency">
       <calculatedColumnFormula>SUM(tblInvestment11[[#This Row],[JAN]:[DEC]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{87EBC5D5-E6EE-1C40-9266-76AE68FD5A68}" name="AVG" totalsRowFunction="sum" dataDxfId="5" totalsRowDxfId="4" dataCellStyle="Currency">
+    <tableColumn id="17" xr3:uid="{87EBC5D5-E6EE-1C40-9266-76AE68FD5A68}" name="AVG" totalsRowFunction="sum" dataDxfId="19" totalsRowDxfId="2" dataCellStyle="Currency">
       <calculatedColumnFormula>AVERAGEIF(tblInvestment11[[#This Row],[JAN]:[DEC]],"&gt;=0")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{19F050A6-4569-D54D-B761-D1AA987ED540}" name="MED" totalsRowFunction="sum" dataDxfId="3" totalsRowDxfId="2" dataCellStyle="Currency">
+    <tableColumn id="16" xr3:uid="{19F050A6-4569-D54D-B761-D1AA987ED540}" name="MED" totalsRowFunction="sum" dataDxfId="18" totalsRowDxfId="1" dataCellStyle="Currency">
       <calculatedColumnFormula>MEDIAN(tblInvestment11[[#This Row],[JAN]:[DEC]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{898DD70E-5E50-5847-B391-F60D3CE918FB}" name="SPARKLINE" dataDxfId="1" totalsRowDxfId="0"/>
+    <tableColumn id="15" xr3:uid="{898DD70E-5E50-5847-B391-F60D3CE918FB}" name="SPARKLINE" dataDxfId="17" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Table Style 1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="1"/>
   <extLst>
@@ -4258,8 +4255,9 @@
       <c r="AK1" s="4"/>
     </row>
     <row r="2" spans="1:37" ht="126" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="41" t="s">
-        <v>53</v>
+      <c r="B2" s="41" t="str">
+        <f ca="1">"BUDGET "&amp;YEAR(TODAY())</f>
+        <v>BUDGET 2026</v>
       </c>
       <c r="C2" s="41"/>
       <c r="D2" s="41"/>
@@ -6147,14 +6145,38 @@
       <c r="B37" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C37" s="23"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
-      <c r="H37" s="23"/>
-      <c r="I37" s="23"/>
-      <c r="J37" s="23"/>
+      <c r="C37" s="23">
+        <f>SUBTOTAL(109,tblInvestment11[JAN])</f>
+        <v>0</v>
+      </c>
+      <c r="D37" s="23">
+        <f>SUBTOTAL(109,tblInvestment11[FEB])</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="23">
+        <f>SUBTOTAL(109,tblInvestment11[MAR])</f>
+        <v>0</v>
+      </c>
+      <c r="F37" s="23">
+        <f>SUBTOTAL(109,tblInvestment11[APR])</f>
+        <v>0</v>
+      </c>
+      <c r="G37" s="23">
+        <f>SUBTOTAL(109,tblInvestment11[MAY])</f>
+        <v>0</v>
+      </c>
+      <c r="H37" s="23">
+        <f>SUBTOTAL(109,tblInvestment11[JUN])</f>
+        <v>0</v>
+      </c>
+      <c r="I37" s="23">
+        <f>SUBTOTAL(109,tblInvestment11[JUL])</f>
+        <v>0</v>
+      </c>
+      <c r="J37" s="23">
+        <f>SUBTOTAL(109,tblInvestment11[AUG])</f>
+        <v>0</v>
+      </c>
       <c r="K37" s="23">
         <f>SUBTOTAL(109,tblInvestment11[SEP])</f>
         <v>0</v>
@@ -9826,7 +9848,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
       <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1" xr2:uid="{A51D215C-6A0C-D443-9A45-6910023EF5F6}">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1" xr2:uid="{684D059B-A148-7B4D-9E6A-6A758AEBB88C}">
           <x14:colorSeries theme="4" tint="-0.499984740745262"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -9837,104 +9859,40 @@
           <x14:colorLow theme="4"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>Sheet1!C6:N6</xm:f>
-              <xm:sqref>R6</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>Sheet1!C7:N7</xm:f>
-              <xm:sqref>R7</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>Sheet1!C8:N8</xm:f>
-              <xm:sqref>R8</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>Sheet1!C9:N9</xm:f>
-              <xm:sqref>R9</xm:sqref>
+              <xm:f>Sheet1!C21:N21</xm:f>
+              <xm:sqref>R21</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1" xr2:uid="{382C768D-DF9D-8946-BAD3-24209AB66791}">
-          <x14:colorSeries theme="4" tint="-0.499984740745262"/>
-          <x14:colorNegative theme="5"/>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" markers="1" high="1" low="1" xr2:uid="{3489094E-86F0-554F-8EA5-9E9DAEA9CAA8}">
+          <x14:colorSeries theme="0"/>
+          <x14:colorNegative theme="6"/>
           <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
-          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
-          <x14:colorLast theme="4" tint="0.39997558519241921"/>
-          <x14:colorHigh theme="4"/>
-          <x14:colorLow theme="4"/>
+          <x14:colorMarkers theme="0"/>
+          <x14:colorFirst theme="5" tint="0.39997558519241921"/>
+          <x14:colorLast theme="5" tint="0.39997558519241921"/>
+          <x14:colorHigh theme="5"/>
+          <x14:colorLow theme="5"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>Sheet1!C12:N12</xm:f>
-              <xm:sqref>R12</xm:sqref>
+              <xm:f>Sheet1!C40:N40</xm:f>
+              <xm:sqref>R40</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C13:N13</xm:f>
-              <xm:sqref>R13</xm:sqref>
+              <xm:f>Sheet1!C41:N41</xm:f>
+              <xm:sqref>R41</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C14:N14</xm:f>
-              <xm:sqref>R14</xm:sqref>
+              <xm:f>Sheet1!C42:N42</xm:f>
+              <xm:sqref>R42</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C15:N15</xm:f>
-              <xm:sqref>R15</xm:sqref>
+              <xm:f>Sheet1!C43:N43</xm:f>
+              <xm:sqref>R43</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C16:N16</xm:f>
-              <xm:sqref>R16</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>Sheet1!C17:N17</xm:f>
-              <xm:sqref>R17</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>Sheet1!C18:N18</xm:f>
-              <xm:sqref>R18</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>Sheet1!C19:N19</xm:f>
-              <xm:sqref>R19</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>Sheet1!C20:N20</xm:f>
-              <xm:sqref>R20</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1" xr2:uid="{91D187D6-5323-544B-B7BE-ABB6200C5BA5}">
-          <x14:colorSeries theme="4" tint="-0.499984740745262"/>
-          <x14:colorNegative theme="5"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
-          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
-          <x14:colorLast theme="4" tint="0.39997558519241921"/>
-          <x14:colorHigh theme="4"/>
-          <x14:colorLow theme="4"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>Sheet1!C33:N33</xm:f>
-              <xm:sqref>R33</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1" xr2:uid="{E5835441-2CEF-4A46-B3DA-A71702CCB74C}">
-          <x14:colorSeries theme="4" tint="-0.499984740745262"/>
-          <x14:colorNegative theme="5"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
-          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
-          <x14:colorLast theme="4" tint="0.39997558519241921"/>
-          <x14:colorHigh theme="4"/>
-          <x14:colorLow theme="4"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>Sheet1!C36:N36</xm:f>
-              <xm:sqref>R36</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>Sheet1!C37:N37</xm:f>
-              <xm:sqref>R37</xm:sqref>
+              <xm:f>Sheet1!C44:N44</xm:f>
+              <xm:sqref>R44</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
@@ -9990,39 +9948,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" markers="1" high="1" low="1" xr2:uid="{3489094E-86F0-554F-8EA5-9E9DAEA9CAA8}">
-          <x14:colorSeries theme="0"/>
-          <x14:colorNegative theme="6"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers theme="0"/>
-          <x14:colorFirst theme="5" tint="0.39997558519241921"/>
-          <x14:colorLast theme="5" tint="0.39997558519241921"/>
-          <x14:colorHigh theme="5"/>
-          <x14:colorLow theme="5"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>Sheet1!C40:N40</xm:f>
-              <xm:sqref>R40</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>Sheet1!C41:N41</xm:f>
-              <xm:sqref>R41</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>Sheet1!C42:N42</xm:f>
-              <xm:sqref>R42</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>Sheet1!C43:N43</xm:f>
-              <xm:sqref>R43</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>Sheet1!C44:N44</xm:f>
-              <xm:sqref>R44</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1" xr2:uid="{684D059B-A148-7B4D-9E6A-6A758AEBB88C}">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1" xr2:uid="{E5835441-2CEF-4A46-B3DA-A71702CCB74C}">
           <x14:colorSeries theme="4" tint="-0.499984740745262"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -10033,8 +9959,104 @@
           <x14:colorLow theme="4"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>Sheet1!C21:N21</xm:f>
-              <xm:sqref>R21</xm:sqref>
+              <xm:f>Sheet1!C36:N36</xm:f>
+              <xm:sqref>R36</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!C37:N37</xm:f>
+              <xm:sqref>R37</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1" xr2:uid="{91D187D6-5323-544B-B7BE-ABB6200C5BA5}">
+          <x14:colorSeries theme="4" tint="-0.499984740745262"/>
+          <x14:colorNegative theme="5"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
+          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
+          <x14:colorLast theme="4" tint="0.39997558519241921"/>
+          <x14:colorHigh theme="4"/>
+          <x14:colorLow theme="4"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Sheet1!C33:N33</xm:f>
+              <xm:sqref>R33</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1" xr2:uid="{382C768D-DF9D-8946-BAD3-24209AB66791}">
+          <x14:colorSeries theme="4" tint="-0.499984740745262"/>
+          <x14:colorNegative theme="5"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
+          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
+          <x14:colorLast theme="4" tint="0.39997558519241921"/>
+          <x14:colorHigh theme="4"/>
+          <x14:colorLow theme="4"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Sheet1!C12:N12</xm:f>
+              <xm:sqref>R12</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!C13:N13</xm:f>
+              <xm:sqref>R13</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!C14:N14</xm:f>
+              <xm:sqref>R14</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!C15:N15</xm:f>
+              <xm:sqref>R15</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!C16:N16</xm:f>
+              <xm:sqref>R16</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!C17:N17</xm:f>
+              <xm:sqref>R17</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!C18:N18</xm:f>
+              <xm:sqref>R18</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!C19:N19</xm:f>
+              <xm:sqref>R19</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!C20:N20</xm:f>
+              <xm:sqref>R20</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1" xr2:uid="{A51D215C-6A0C-D443-9A45-6910023EF5F6}">
+          <x14:colorSeries theme="4" tint="-0.499984740745262"/>
+          <x14:colorNegative theme="5"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
+          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
+          <x14:colorLast theme="4" tint="0.39997558519241921"/>
+          <x14:colorHigh theme="4"/>
+          <x14:colorLow theme="4"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Sheet1!C6:N6</xm:f>
+              <xm:sqref>R6</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!C7:N7</xm:f>
+              <xm:sqref>R7</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!C8:N8</xm:f>
+              <xm:sqref>R8</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!C9:N9</xm:f>
+              <xm:sqref>R9</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
@@ -10045,35 +10067,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="28" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="60f5a4f2d2b0abadcf532d48ebf9cb71">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7dd78129e6a1811f84807ad11c651531" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -10385,27 +10378,36 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC9016F9-7015-43E2-8C51-8C9B031A2916}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61C4CF09-E16C-491E-896B-59FA5BAACD58}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5AF2BFB-A3F6-42EF-82A3-18ADC5F181D5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10426,6 +10428,26 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61C4CF09-E16C-491E-896B-59FA5BAACD58}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC9016F9-7015-43E2-8C51-8C9B031A2916}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata"/>
 </file>
--- a/assets/budget-template.xlsx
+++ b/assets/budget-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/taulo/GolandProjects/budgetpipe/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29BD43A-C337-EE4C-AF1F-EA15A41F4A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3FE1EA2-98D3-2B4D-ACC8-8BFC8362D54B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -209,7 +209,7 @@
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
       <sz val="10"/>
       <color theme="1" tint="0.14993743705557422"/>
@@ -589,6 +589,16 @@
     </dxf>
     <dxf>
       <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -606,315 +616,6 @@
       </font>
       <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -960,6 +661,26 @@
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -970,133 +691,412 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3846,7 +3846,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D01C33AF-B39E-7346-82C8-45610BC0ACDD}" name="tblIncome7" displayName="tblIncome7" ref="B5:R9" totalsRowCount="1" headerRowDxfId="165" dataDxfId="164" totalsRowDxfId="163">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D01C33AF-B39E-7346-82C8-45610BC0ACDD}" name="tblIncome" displayName="tblIncome" ref="B5:R9" totalsRowCount="1" headerRowDxfId="165" dataDxfId="164" totalsRowDxfId="163">
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{E570BA2C-7D65-CF4F-AFB0-0208DC5794C9}" name="INCOME" totalsRowLabel="Total" dataDxfId="162" totalsRowDxfId="161"/>
     <tableColumn id="2" xr3:uid="{BF162114-DA3D-4F41-BF11-540DD3FF7370}" name="JAN" totalsRowFunction="sum" dataDxfId="160" totalsRowDxfId="159" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
@@ -3862,13 +3862,13 @@
     <tableColumn id="12" xr3:uid="{617B479F-E8D5-CE4D-A6EB-11AB8DE52EA3}" name="NOV" totalsRowFunction="sum" dataDxfId="140" totalsRowDxfId="139" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
     <tableColumn id="13" xr3:uid="{13A7594F-70B5-894C-B4EC-B5696AC00837}" name="DEC" totalsRowFunction="sum" dataDxfId="138" totalsRowDxfId="137" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
     <tableColumn id="14" xr3:uid="{18BA2D4B-ADA7-8548-8162-803836A47823}" name="TOTAL" totalsRowFunction="sum" dataDxfId="136" totalsRowDxfId="135" dataCellStyle="Currency" totalsRowCellStyle="Currency">
-      <calculatedColumnFormula>SUM(tblIncome7[[#This Row],[JAN]:[DEC]])</calculatedColumnFormula>
+      <calculatedColumnFormula>SUM(tblIncome[[#This Row],[JAN]:[DEC]])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="17" xr3:uid="{C5410515-385A-7D4F-A9CB-44AF95BB9E1E}" name="AVG" totalsRowFunction="sum" dataDxfId="134" totalsRowDxfId="133" dataCellStyle="Currency" totalsRowCellStyle="Currency">
-      <calculatedColumnFormula>AVERAGEIF(tblIncome7[[#This Row],[JAN]:[DEC]],"&gt;=0")</calculatedColumnFormula>
+      <calculatedColumnFormula>AVERAGEIF(tblIncome[[#This Row],[JAN]:[DEC]],"&gt;=0")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" xr3:uid="{259CA5E2-8B26-8F41-89B5-0CFD34C5864A}" name="MED" totalsRowFunction="sum" dataDxfId="132" totalsRowDxfId="131" dataCellStyle="Currency" totalsRowCellStyle="Currency">
-      <calculatedColumnFormula>MEDIAN(tblIncome7[[#This Row],[JAN]:[DEC]])</calculatedColumnFormula>
+      <calculatedColumnFormula>MEDIAN(tblIncome[[#This Row],[JAN]:[DEC]])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="15" xr3:uid="{4E49A019-475D-D141-9175-12A1ABA0CF53}" name="SPARKLINE" dataDxfId="130" totalsRowDxfId="129"/>
   </tableColumns>
@@ -3882,7 +3882,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{66404086-D07C-FE4E-83EA-A9FDEAB39396}" name="tblFixed8" displayName="tblFixed8" ref="B11:R21" totalsRowCount="1" headerRowDxfId="128" dataDxfId="127" totalsRowDxfId="126">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{66404086-D07C-FE4E-83EA-A9FDEAB39396}" name="tblFixed" displayName="tblFixed" ref="B11:R21" totalsRowCount="1" headerRowDxfId="128" dataDxfId="127" totalsRowDxfId="126">
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{7218B040-B89C-704E-89B6-F95A0FB36621}" name="FIXED" totalsRowLabel="Total" dataDxfId="125" totalsRowDxfId="124"/>
     <tableColumn id="2" xr3:uid="{B792F60A-FDCF-674D-AF06-1A5C81AFC928}" name="JAN" totalsRowFunction="sum" dataDxfId="123" totalsRowDxfId="122" dataCellStyle="Currency"/>
@@ -3898,13 +3898,13 @@
     <tableColumn id="12" xr3:uid="{07934322-743A-434A-AAE2-86BF3E6FB493}" name="NOV" totalsRowFunction="sum" dataDxfId="103" totalsRowDxfId="102" dataCellStyle="Currency"/>
     <tableColumn id="13" xr3:uid="{1FFBBD23-0890-344B-8381-0DD3B4758F0B}" name="DEC" totalsRowFunction="sum" dataDxfId="101" totalsRowDxfId="100" dataCellStyle="Currency"/>
     <tableColumn id="14" xr3:uid="{50A875B2-5D80-5641-AECD-98B17E0DC063}" name="TOTAL" totalsRowFunction="sum" dataDxfId="99" totalsRowDxfId="98" dataCellStyle="Currency">
-      <calculatedColumnFormula>SUM(tblFixed8[[#This Row],[JAN]:[DEC]])</calculatedColumnFormula>
+      <calculatedColumnFormula>SUM(tblFixed[[#This Row],[JAN]:[DEC]])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="15" xr3:uid="{CE93D4EA-4453-7C45-A70C-233430B9452C}" name="AVG" totalsRowFunction="sum" dataDxfId="97" totalsRowDxfId="96" dataCellStyle="Currency">
-      <calculatedColumnFormula>AVERAGEIF(tblFixed8[[#This Row],[JAN]:[DEC]],"&lt;=0")</calculatedColumnFormula>
+      <calculatedColumnFormula>AVERAGEIF(tblFixed[[#This Row],[JAN]:[DEC]],"&lt;=0")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" xr3:uid="{CC87E450-EFFE-9A47-8058-E1413EC2CA14}" name="MED" totalsRowFunction="sum" dataDxfId="95" totalsRowDxfId="94" dataCellStyle="Currency">
-      <calculatedColumnFormula>MEDIAN(tblFixed8[[#This Row],[JAN]:[DEC]])</calculatedColumnFormula>
+      <calculatedColumnFormula>MEDIAN(tblFixed[[#This Row],[JAN]:[DEC]])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="17" xr3:uid="{2FF721F3-FC7D-E34A-A6AA-092EA0B357BE}" name="SPARKLINE" dataDxfId="93" totalsRowDxfId="92" dataCellStyle="Currency"/>
   </tableColumns>
@@ -3918,7 +3918,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{6569D38E-6245-AE4B-A792-59BF998FDE54}" name="tblVariable9" displayName="tblVariable9" ref="B22:R33" totalsRowCount="1" headerRowDxfId="91" dataDxfId="90" totalsRowDxfId="89">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{6569D38E-6245-AE4B-A792-59BF998FDE54}" name="tblVariable" displayName="tblVariable" ref="B22:R33" totalsRowCount="1" headerRowDxfId="91" dataDxfId="90" totalsRowDxfId="89">
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{2DFD2C0E-6649-0444-8936-6E4F63A7A5A6}" name="VARIABLE" totalsRowLabel="Total" dataDxfId="88" totalsRowDxfId="87"/>
     <tableColumn id="2" xr3:uid="{C7391998-5A09-F747-9D32-1884CA05F01B}" name="JAN" totalsRowFunction="sum" dataDxfId="86" totalsRowDxfId="85" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
@@ -3934,13 +3934,13 @@
     <tableColumn id="12" xr3:uid="{F5CBFD5A-01B2-A543-B75C-F9CF31C043F8}" name="NOV" totalsRowFunction="sum" dataDxfId="66" totalsRowDxfId="65" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
     <tableColumn id="13" xr3:uid="{FD758FA9-E23C-ED4A-B63D-54AE803A68C7}" name="DEC" totalsRowFunction="sum" dataDxfId="64" totalsRowDxfId="63" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
     <tableColumn id="14" xr3:uid="{A640743B-4AC6-E44B-B519-E4E20EDFD578}" name="TOTAL" totalsRowFunction="sum" dataDxfId="62" totalsRowDxfId="61" dataCellStyle="Currency" totalsRowCellStyle="Currency">
-      <calculatedColumnFormula>SUM(tblVariable9[[#This Row],[JAN]:[DEC]])</calculatedColumnFormula>
+      <calculatedColumnFormula>SUM(tblVariable[[#This Row],[JAN]:[DEC]])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="15" xr3:uid="{CAF20004-DD01-2845-A797-9EB80A1CA007}" name="AVG" totalsRowFunction="sum" dataDxfId="60" totalsRowDxfId="59" dataCellStyle="Currency" totalsRowCellStyle="Currency">
-      <calculatedColumnFormula>AVERAGEIF(tblVariable9[[#This Row],[JAN]:[DEC]],"&lt;=0")</calculatedColumnFormula>
+      <calculatedColumnFormula>AVERAGEIF(tblVariable[[#This Row],[JAN]:[DEC]],"&lt;=0")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="17" xr3:uid="{F510BBB5-5E81-6D49-B4F6-7B828907F237}" name="MED" totalsRowFunction="sum" dataDxfId="58" totalsRowDxfId="57" dataCellStyle="Currency" totalsRowCellStyle="Currency">
-      <calculatedColumnFormula>MEDIAN(tblVariable9[[#This Row],[JAN]:[DEC]])</calculatedColumnFormula>
+      <calculatedColumnFormula>MEDIAN(tblVariable[[#This Row],[JAN]:[DEC]])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="18" xr3:uid="{5D351838-4696-3B44-8E25-A2783BDE825F}" name="SPARKLINE" dataDxfId="56" totalsRowDxfId="55" dataCellStyle="Currency"/>
   </tableColumns>
@@ -3954,7 +3954,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{B54D96C8-B74E-2946-B4C2-8B65E37B1DEF}" name="tblTotals510" displayName="tblTotals510" ref="B39:R44" totalsRowShown="0" dataDxfId="54" headerRowCellStyle="Accent1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{B54D96C8-B74E-2946-B4C2-8B65E37B1DEF}" name="tblTotals" displayName="tblTotals" ref="B39:R44" totalsRowShown="0" dataDxfId="54" headerRowCellStyle="Accent1">
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{AEB778AB-6508-6F41-B6C8-9970D4E1F6BA}" name="TOTALS" dataDxfId="53" dataCellStyle="Accent4"/>
     <tableColumn id="2" xr3:uid="{ECBCEAF6-76F1-8C49-8B6D-BC553DC21645}" name="JAN" dataDxfId="52" dataCellStyle="Accent1"/>
@@ -3984,31 +3984,31 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{992450C3-516C-E54A-8E9D-60C940989794}" name="tblInvestment11" displayName="tblInvestment11" ref="B35:R37" totalsRowCount="1" headerRowDxfId="36" dataDxfId="35" totalsRowDxfId="34">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{992450C3-516C-E54A-8E9D-60C940989794}" name="tblInvestment" displayName="tblInvestment" ref="B35:R37" totalsRowCount="1" headerRowDxfId="36" dataDxfId="35" totalsRowDxfId="34">
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{294014AF-D891-F449-B566-7F4086B30F5D}" name="INVESTMENT" totalsRowLabel="Total" dataDxfId="33" totalsRowDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{15C43410-3504-934F-9BE6-940C4BC3EB1C}" name="JAN" totalsRowFunction="sum" dataDxfId="32" totalsRowDxfId="15" dataCellStyle="Currency"/>
-    <tableColumn id="3" xr3:uid="{313B1E83-6D0C-3947-AB16-91A5B56D7B46}" name="FEB" totalsRowFunction="sum" dataDxfId="31" totalsRowDxfId="14" dataCellStyle="Currency"/>
-    <tableColumn id="4" xr3:uid="{9C5E5D1F-F6CE-2143-99A3-AD994D06E5AF}" name="MAR" totalsRowFunction="sum" dataDxfId="30" totalsRowDxfId="13" dataCellStyle="Currency"/>
-    <tableColumn id="5" xr3:uid="{C3E012AE-4AAD-2146-AF94-58319121E8DD}" name="APR" totalsRowFunction="sum" dataDxfId="29" totalsRowDxfId="12" dataCellStyle="Currency"/>
-    <tableColumn id="6" xr3:uid="{577F144F-51EC-AB4B-AF91-E945C4A1B2BC}" name="MAY" totalsRowFunction="sum" dataDxfId="28" totalsRowDxfId="11" dataCellStyle="Currency"/>
-    <tableColumn id="7" xr3:uid="{DCDB89FE-34A0-4D4E-9201-C3623E2F8896}" name="JUN" totalsRowFunction="sum" dataDxfId="27" totalsRowDxfId="10" dataCellStyle="Currency"/>
-    <tableColumn id="8" xr3:uid="{2A44951E-CCCB-0447-91FA-68374BB208D0}" name="JUL" totalsRowFunction="sum" dataDxfId="26" totalsRowDxfId="9" dataCellStyle="Currency"/>
-    <tableColumn id="9" xr3:uid="{694F199B-9ABA-D54F-95D4-E62D55AE340D}" name="AUG" totalsRowFunction="sum" dataDxfId="25" totalsRowDxfId="8" dataCellStyle="Currency"/>
-    <tableColumn id="10" xr3:uid="{73668DD0-3192-F74F-A607-7282D6844B79}" name="SEP" totalsRowFunction="sum" dataDxfId="24" totalsRowDxfId="7" dataCellStyle="Currency"/>
-    <tableColumn id="11" xr3:uid="{D1F09B50-63EF-954F-A630-252B118F69BD}" name="OCT" totalsRowFunction="sum" dataDxfId="23" totalsRowDxfId="6" dataCellStyle="Currency"/>
-    <tableColumn id="12" xr3:uid="{32F0E92C-55F7-984F-9A71-48FE200865C7}" name="NOV" totalsRowFunction="sum" dataDxfId="22" totalsRowDxfId="5" dataCellStyle="Currency"/>
-    <tableColumn id="13" xr3:uid="{41E80EA4-43CB-B740-99FD-F01662477345}" name="DEC" totalsRowFunction="sum" dataDxfId="21" totalsRowDxfId="4" dataCellStyle="Currency"/>
-    <tableColumn id="14" xr3:uid="{3440B9C2-E91C-414C-96C9-BDFF292029FB}" name="TOTAL" totalsRowFunction="sum" dataDxfId="20" totalsRowDxfId="3" dataCellStyle="Currency">
-      <calculatedColumnFormula>SUM(tblInvestment11[[#This Row],[JAN]:[DEC]])</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{294014AF-D891-F449-B566-7F4086B30F5D}" name="INVESTMENT" totalsRowLabel="Total" dataDxfId="33" totalsRowDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{15C43410-3504-934F-9BE6-940C4BC3EB1C}" name="JAN" totalsRowFunction="sum" dataDxfId="31" totalsRowDxfId="30" dataCellStyle="Currency"/>
+    <tableColumn id="3" xr3:uid="{313B1E83-6D0C-3947-AB16-91A5B56D7B46}" name="FEB" totalsRowFunction="sum" dataDxfId="29" totalsRowDxfId="28" dataCellStyle="Currency"/>
+    <tableColumn id="4" xr3:uid="{9C5E5D1F-F6CE-2143-99A3-AD994D06E5AF}" name="MAR" totalsRowFunction="sum" dataDxfId="27" totalsRowDxfId="26" dataCellStyle="Currency"/>
+    <tableColumn id="5" xr3:uid="{C3E012AE-4AAD-2146-AF94-58319121E8DD}" name="APR" totalsRowFunction="sum" dataDxfId="25" totalsRowDxfId="24" dataCellStyle="Currency"/>
+    <tableColumn id="6" xr3:uid="{577F144F-51EC-AB4B-AF91-E945C4A1B2BC}" name="MAY" totalsRowFunction="sum" dataDxfId="23" totalsRowDxfId="22" dataCellStyle="Currency"/>
+    <tableColumn id="7" xr3:uid="{DCDB89FE-34A0-4D4E-9201-C3623E2F8896}" name="JUN" totalsRowFunction="sum" dataDxfId="21" totalsRowDxfId="20" dataCellStyle="Currency"/>
+    <tableColumn id="8" xr3:uid="{2A44951E-CCCB-0447-91FA-68374BB208D0}" name="JUL" totalsRowFunction="sum" dataDxfId="19" totalsRowDxfId="18" dataCellStyle="Currency"/>
+    <tableColumn id="9" xr3:uid="{694F199B-9ABA-D54F-95D4-E62D55AE340D}" name="AUG" totalsRowFunction="sum" dataDxfId="17" totalsRowDxfId="16" dataCellStyle="Currency"/>
+    <tableColumn id="10" xr3:uid="{73668DD0-3192-F74F-A607-7282D6844B79}" name="SEP" totalsRowFunction="sum" dataDxfId="15" totalsRowDxfId="14" dataCellStyle="Currency"/>
+    <tableColumn id="11" xr3:uid="{D1F09B50-63EF-954F-A630-252B118F69BD}" name="OCT" totalsRowFunction="sum" dataDxfId="13" totalsRowDxfId="12" dataCellStyle="Currency"/>
+    <tableColumn id="12" xr3:uid="{32F0E92C-55F7-984F-9A71-48FE200865C7}" name="NOV" totalsRowFunction="sum" dataDxfId="11" totalsRowDxfId="10" dataCellStyle="Currency"/>
+    <tableColumn id="13" xr3:uid="{41E80EA4-43CB-B740-99FD-F01662477345}" name="DEC" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="8" dataCellStyle="Currency"/>
+    <tableColumn id="14" xr3:uid="{3440B9C2-E91C-414C-96C9-BDFF292029FB}" name="TOTAL" totalsRowFunction="sum" dataDxfId="7" totalsRowDxfId="6" dataCellStyle="Currency">
+      <calculatedColumnFormula>SUM(tblInvestment[[#This Row],[JAN]:[DEC]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{87EBC5D5-E6EE-1C40-9266-76AE68FD5A68}" name="AVG" totalsRowFunction="sum" dataDxfId="19" totalsRowDxfId="2" dataCellStyle="Currency">
-      <calculatedColumnFormula>AVERAGEIF(tblInvestment11[[#This Row],[JAN]:[DEC]],"&gt;=0")</calculatedColumnFormula>
+    <tableColumn id="17" xr3:uid="{87EBC5D5-E6EE-1C40-9266-76AE68FD5A68}" name="AVG" totalsRowFunction="sum" dataDxfId="5" totalsRowDxfId="4" dataCellStyle="Currency">
+      <calculatedColumnFormula>AVERAGEIF(tblInvestment[[#This Row],[JAN]:[DEC]],"&gt;=0")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{19F050A6-4569-D54D-B761-D1AA987ED540}" name="MED" totalsRowFunction="sum" dataDxfId="18" totalsRowDxfId="1" dataCellStyle="Currency">
-      <calculatedColumnFormula>MEDIAN(tblInvestment11[[#This Row],[JAN]:[DEC]])</calculatedColumnFormula>
+    <tableColumn id="16" xr3:uid="{19F050A6-4569-D54D-B761-D1AA987ED540}" name="MED" totalsRowFunction="sum" dataDxfId="3" totalsRowDxfId="2" dataCellStyle="Currency">
+      <calculatedColumnFormula>MEDIAN(tblInvestment[[#This Row],[JAN]:[DEC]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{898DD70E-5E50-5847-B391-F60D3CE918FB}" name="SPARKLINE" dataDxfId="17" totalsRowDxfId="0"/>
+    <tableColumn id="15" xr3:uid="{898DD70E-5E50-5847-B391-F60D3CE918FB}" name="SPARKLINE" dataDxfId="1" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Table Style 1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="1"/>
   <extLst>
@@ -4215,7 +4215,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F51B55-1F0E-724E-B364-79BB2AAE95EA}">
   <dimension ref="A1:AK128"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="6.83203125" style="3" customWidth="1"/>
     <col min="2" max="2" width="38.6640625" style="4" customWidth="1"/>
@@ -4232,7 +4232,7 @@
     <col min="19" max="16384" width="8.83203125" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:37" ht="35" customHeight="1">
       <c r="R1" s="4"/>
       <c r="S1" s="4"/>
       <c r="T1" s="4"/>
@@ -4254,7 +4254,7 @@
       <c r="AJ1" s="4"/>
       <c r="AK1" s="4"/>
     </row>
-    <row r="2" spans="1:37" ht="126" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:37" ht="126" customHeight="1">
       <c r="B2" s="41" t="str">
         <f ca="1">"BUDGET "&amp;YEAR(TODAY())</f>
         <v>BUDGET 2026</v>
@@ -4295,7 +4295,7 @@
       <c r="AJ2" s="4"/>
       <c r="AK2" s="4"/>
     </row>
-    <row r="3" spans="1:37" ht="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:37" ht="1" customHeight="1">
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
@@ -4317,7 +4317,7 @@
       <c r="AJ3" s="4"/>
       <c r="AK3" s="4"/>
     </row>
-    <row r="4" spans="1:37" s="15" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:37" s="15" customFormat="1" ht="35" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="36" t="s">
         <v>0</v>
@@ -4358,7 +4358,7 @@
       <c r="AJ4" s="4"/>
       <c r="AK4" s="4"/>
     </row>
-    <row r="5" spans="1:37" s="2" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:37" s="2" customFormat="1" ht="35" customHeight="1">
       <c r="A5" s="6"/>
       <c r="B5" s="12" t="s">
         <v>1</v>
@@ -4431,7 +4431,7 @@
       <c r="AJ5" s="4"/>
       <c r="AK5" s="4"/>
     </row>
-    <row r="6" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
         <v>40</v>
@@ -4449,15 +4449,15 @@
       <c r="M6" s="22"/>
       <c r="N6" s="22"/>
       <c r="O6" s="22">
-        <f>SUM(tblIncome7[[#This Row],[JAN]:[DEC]])</f>
+        <f>SUM(tblIncome[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="P6" s="22" t="e">
-        <f>AVERAGEIF(tblIncome7[[#This Row],[JAN]:[DEC]],"&gt;=0")</f>
+        <f>AVERAGEIF(tblIncome[[#This Row],[JAN]:[DEC]],"&gt;=0")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q6" s="22" t="e">
-        <f>MEDIAN(tblIncome7[[#This Row],[JAN]:[DEC]])</f>
+        <f>MEDIAN(tblIncome[[#This Row],[JAN]:[DEC]])</f>
         <v>#NUM!</v>
       </c>
       <c r="R6" s="8"/>
@@ -4481,7 +4481,7 @@
       <c r="AJ6" s="4"/>
       <c r="AK6" s="4"/>
     </row>
-    <row r="7" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A7" s="6"/>
       <c r="B7" s="7" t="s">
         <v>41</v>
@@ -4499,15 +4499,15 @@
       <c r="M7" s="22"/>
       <c r="N7" s="22"/>
       <c r="O7" s="22">
-        <f>SUM(tblIncome7[[#This Row],[JAN]:[DEC]])</f>
+        <f>SUM(tblIncome[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="P7" s="22" t="e">
-        <f>AVERAGEIF(tblIncome7[[#This Row],[JAN]:[DEC]],"&gt;=0")</f>
+        <f>AVERAGEIF(tblIncome[[#This Row],[JAN]:[DEC]],"&gt;=0")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q7" s="22" t="e">
-        <f>MEDIAN(tblIncome7[[#This Row],[JAN]:[DEC]])</f>
+        <f>MEDIAN(tblIncome[[#This Row],[JAN]:[DEC]])</f>
         <v>#NUM!</v>
       </c>
       <c r="R7" s="8"/>
@@ -4531,7 +4531,7 @@
       <c r="AJ7" s="4"/>
       <c r="AK7" s="4"/>
     </row>
-    <row r="8" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A8" s="6"/>
       <c r="B8" s="7" t="s">
         <v>42</v>
@@ -4549,15 +4549,15 @@
       <c r="M8" s="22"/>
       <c r="N8" s="22"/>
       <c r="O8" s="22">
-        <f>SUM(tblIncome7[[#This Row],[JAN]:[DEC]])</f>
+        <f>SUM(tblIncome[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="P8" s="22" t="e">
-        <f>AVERAGEIF(tblIncome7[[#This Row],[JAN]:[DEC]],"&gt;=0")</f>
+        <f>AVERAGEIF(tblIncome[[#This Row],[JAN]:[DEC]],"&gt;=0")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q8" s="22" t="e">
-        <f>MEDIAN(tblIncome7[[#This Row],[JAN]:[DEC]])</f>
+        <f>MEDIAN(tblIncome[[#This Row],[JAN]:[DEC]])</f>
         <v>#NUM!</v>
       </c>
       <c r="R8" s="8"/>
@@ -4581,69 +4581,69 @@
       <c r="AJ8" s="4"/>
       <c r="AK8" s="4"/>
     </row>
-    <row r="9" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A9" s="6"/>
       <c r="B9" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="22">
-        <f>SUBTOTAL(109,tblIncome7[JAN])</f>
+        <f>SUBTOTAL(109,tblIncome[JAN])</f>
         <v>0</v>
       </c>
       <c r="D9" s="22">
-        <f>SUBTOTAL(109,tblIncome7[FEB])</f>
+        <f>SUBTOTAL(109,tblIncome[FEB])</f>
         <v>0</v>
       </c>
       <c r="E9" s="22">
-        <f>SUBTOTAL(109,tblIncome7[MAR])</f>
+        <f>SUBTOTAL(109,tblIncome[MAR])</f>
         <v>0</v>
       </c>
       <c r="F9" s="22">
-        <f>SUBTOTAL(109,tblIncome7[APR])</f>
+        <f>SUBTOTAL(109,tblIncome[APR])</f>
         <v>0</v>
       </c>
       <c r="G9" s="22">
-        <f>SUBTOTAL(109,tblIncome7[MAY])</f>
+        <f>SUBTOTAL(109,tblIncome[MAY])</f>
         <v>0</v>
       </c>
       <c r="H9" s="22">
-        <f>SUBTOTAL(109,tblIncome7[JUN])</f>
+        <f>SUBTOTAL(109,tblIncome[JUN])</f>
         <v>0</v>
       </c>
       <c r="I9" s="22">
-        <f>SUBTOTAL(109,tblIncome7[JUL])</f>
+        <f>SUBTOTAL(109,tblIncome[JUL])</f>
         <v>0</v>
       </c>
       <c r="J9" s="22">
-        <f>SUBTOTAL(109,tblIncome7[AUG])</f>
+        <f>SUBTOTAL(109,tblIncome[AUG])</f>
         <v>0</v>
       </c>
       <c r="K9" s="22">
-        <f>SUBTOTAL(109,tblIncome7[SEP])</f>
+        <f>SUBTOTAL(109,tblIncome[SEP])</f>
         <v>0</v>
       </c>
       <c r="L9" s="22">
-        <f>SUBTOTAL(109,tblIncome7[OCT])</f>
+        <f>SUBTOTAL(109,tblIncome[OCT])</f>
         <v>0</v>
       </c>
       <c r="M9" s="22">
-        <f>SUBTOTAL(109,tblIncome7[NOV])</f>
+        <f>SUBTOTAL(109,tblIncome[NOV])</f>
         <v>0</v>
       </c>
       <c r="N9" s="22">
-        <f>SUBTOTAL(109,tblIncome7[DEC])</f>
+        <f>SUBTOTAL(109,tblIncome[DEC])</f>
         <v>0</v>
       </c>
       <c r="O9" s="22">
-        <f>SUBTOTAL(109,tblIncome7[TOTAL])</f>
+        <f>SUBTOTAL(109,tblIncome[TOTAL])</f>
         <v>0</v>
       </c>
       <c r="P9" s="22" t="e">
-        <f>SUBTOTAL(109,tblIncome7[AVG])</f>
+        <f>SUBTOTAL(109,tblIncome[AVG])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q9" s="22" t="e">
-        <f>SUBTOTAL(109,tblIncome7[MED])</f>
+        <f>SUBTOTAL(109,tblIncome[MED])</f>
         <v>#NUM!</v>
       </c>
       <c r="R9" s="9"/>
@@ -4667,7 +4667,7 @@
       <c r="AJ9" s="4"/>
       <c r="AK9" s="4"/>
     </row>
-    <row r="10" spans="1:37" s="19" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37" s="19" customFormat="1" ht="35" customHeight="1">
       <c r="A10" s="16"/>
       <c r="B10" s="35" t="s">
         <v>16</v>
@@ -4708,7 +4708,7 @@
       <c r="AJ10" s="4"/>
       <c r="AK10" s="4"/>
     </row>
-    <row r="11" spans="1:37" s="2" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:37" s="2" customFormat="1" ht="35" customHeight="1">
       <c r="A11" s="6"/>
       <c r="B11" s="12" t="s">
         <v>19</v>
@@ -4781,7 +4781,7 @@
       <c r="AJ11" s="4"/>
       <c r="AK11" s="4"/>
     </row>
-    <row r="12" spans="1:37" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:37" s="2" customFormat="1" ht="21" customHeight="1">
       <c r="A12" s="6"/>
       <c r="B12" s="7" t="s">
         <v>21</v>
@@ -4799,15 +4799,15 @@
       <c r="M12" s="22"/>
       <c r="N12" s="22"/>
       <c r="O12" s="22">
-        <f>SUM(tblFixed8[[#This Row],[JAN]:[DEC]])</f>
+        <f>SUM(tblFixed[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="P12" s="22" t="e">
-        <f>AVERAGEIF(tblFixed8[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
+        <f>AVERAGEIF(tblFixed[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q12" s="22" t="e">
-        <f>MEDIAN(tblFixed8[[#This Row],[JAN]:[DEC]])</f>
+        <f>MEDIAN(tblFixed[[#This Row],[JAN]:[DEC]])</f>
         <v>#NUM!</v>
       </c>
       <c r="R12" s="8"/>
@@ -4831,7 +4831,7 @@
       <c r="AJ12" s="4"/>
       <c r="AK12" s="4"/>
     </row>
-    <row r="13" spans="1:37" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:37" s="2" customFormat="1" ht="21" customHeight="1">
       <c r="A13" s="6"/>
       <c r="B13" s="7" t="s">
         <v>22</v>
@@ -4849,15 +4849,15 @@
       <c r="M13" s="22"/>
       <c r="N13" s="22"/>
       <c r="O13" s="22">
-        <f>SUM(tblFixed8[[#This Row],[JAN]:[DEC]])</f>
+        <f>SUM(tblFixed[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="P13" s="24" t="e">
-        <f>AVERAGEIF(tblFixed8[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
+        <f>AVERAGEIF(tblFixed[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q13" s="22" t="e">
-        <f>MEDIAN(tblFixed8[[#This Row],[JAN]:[DEC]])</f>
+        <f>MEDIAN(tblFixed[[#This Row],[JAN]:[DEC]])</f>
         <v>#NUM!</v>
       </c>
       <c r="R13" s="26"/>
@@ -4881,7 +4881,7 @@
       <c r="AJ13" s="4"/>
       <c r="AK13" s="4"/>
     </row>
-    <row r="14" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="7" t="s">
         <v>23</v>
@@ -4899,15 +4899,15 @@
       <c r="M14" s="22"/>
       <c r="N14" s="22"/>
       <c r="O14" s="22">
-        <f>SUM(tblFixed8[[#This Row],[JAN]:[DEC]])</f>
+        <f>SUM(tblFixed[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="P14" s="24" t="e">
-        <f>AVERAGEIF(tblFixed8[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
+        <f>AVERAGEIF(tblFixed[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q14" s="22" t="e">
-        <f>MEDIAN(tblFixed8[[#This Row],[JAN]:[DEC]])</f>
+        <f>MEDIAN(tblFixed[[#This Row],[JAN]:[DEC]])</f>
         <v>#NUM!</v>
       </c>
       <c r="R14" s="8"/>
@@ -4931,7 +4931,7 @@
       <c r="AJ14" s="4"/>
       <c r="AK14" s="4"/>
     </row>
-    <row r="15" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A15" s="3"/>
       <c r="B15" s="7" t="s">
         <v>24</v>
@@ -4949,15 +4949,15 @@
       <c r="M15" s="22"/>
       <c r="N15" s="22"/>
       <c r="O15" s="22">
-        <f>SUM(tblFixed8[[#This Row],[JAN]:[DEC]])</f>
+        <f>SUM(tblFixed[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="P15" s="24" t="e">
-        <f>AVERAGEIF(tblFixed8[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
+        <f>AVERAGEIF(tblFixed[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q15" s="22" t="e">
-        <f>MEDIAN(tblFixed8[[#This Row],[JAN]:[DEC]])</f>
+        <f>MEDIAN(tblFixed[[#This Row],[JAN]:[DEC]])</f>
         <v>#NUM!</v>
       </c>
       <c r="R15" s="8"/>
@@ -4981,7 +4981,7 @@
       <c r="AJ15" s="4"/>
       <c r="AK15" s="4"/>
     </row>
-    <row r="16" spans="1:37" ht="22.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" ht="22.25" customHeight="1">
       <c r="A16" s="11"/>
       <c r="B16" s="7" t="s">
         <v>25</v>
@@ -4999,15 +4999,15 @@
       <c r="M16" s="22"/>
       <c r="N16" s="22"/>
       <c r="O16" s="22">
-        <f>SUM(tblFixed8[[#This Row],[JAN]:[DEC]])</f>
+        <f>SUM(tblFixed[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="P16" s="24" t="e">
-        <f>AVERAGEIF(tblFixed8[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
+        <f>AVERAGEIF(tblFixed[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q16" s="22" t="e">
-        <f>MEDIAN(tblFixed8[[#This Row],[JAN]:[DEC]])</f>
+        <f>MEDIAN(tblFixed[[#This Row],[JAN]:[DEC]])</f>
         <v>#NUM!</v>
       </c>
       <c r="R16" s="8"/>
@@ -5031,7 +5031,7 @@
       <c r="AJ16" s="4"/>
       <c r="AK16" s="4"/>
     </row>
-    <row r="17" spans="1:37" s="14" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:37" s="14" customFormat="1" ht="22" customHeight="1">
       <c r="A17" s="6"/>
       <c r="B17" s="7" t="s">
         <v>26</v>
@@ -5049,15 +5049,15 @@
       <c r="M17" s="22"/>
       <c r="N17" s="22"/>
       <c r="O17" s="22">
-        <f>SUM(tblFixed8[[#This Row],[JAN]:[DEC]])</f>
+        <f>SUM(tblFixed[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="P17" s="24" t="e">
-        <f>AVERAGEIF(tblFixed8[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
+        <f>AVERAGEIF(tblFixed[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q17" s="22" t="e">
-        <f>MEDIAN(tblFixed8[[#This Row],[JAN]:[DEC]])</f>
+        <f>MEDIAN(tblFixed[[#This Row],[JAN]:[DEC]])</f>
         <v>#NUM!</v>
       </c>
       <c r="R17" s="8"/>
@@ -5081,7 +5081,7 @@
       <c r="AJ17" s="4"/>
       <c r="AK17" s="4"/>
     </row>
-    <row r="18" spans="1:37" s="2" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:37" s="2" customFormat="1" ht="22" customHeight="1">
       <c r="A18" s="6"/>
       <c r="B18" s="7" t="s">
         <v>27</v>
@@ -5099,15 +5099,15 @@
       <c r="M18" s="22"/>
       <c r="N18" s="22"/>
       <c r="O18" s="22">
-        <f>SUM(tblFixed8[[#This Row],[JAN]:[DEC]])</f>
+        <f>SUM(tblFixed[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="P18" s="24" t="e">
-        <f>AVERAGEIF(tblFixed8[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
+        <f>AVERAGEIF(tblFixed[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q18" s="22" t="e">
-        <f>MEDIAN(tblFixed8[[#This Row],[JAN]:[DEC]])</f>
+        <f>MEDIAN(tblFixed[[#This Row],[JAN]:[DEC]])</f>
         <v>#NUM!</v>
       </c>
       <c r="R18" s="8"/>
@@ -5131,7 +5131,7 @@
       <c r="AJ18" s="4"/>
       <c r="AK18" s="4"/>
     </row>
-    <row r="19" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A19" s="6"/>
       <c r="B19" s="7" t="s">
         <v>28</v>
@@ -5149,15 +5149,15 @@
       <c r="M19" s="22"/>
       <c r="N19" s="22"/>
       <c r="O19" s="22">
-        <f>SUM(tblFixed8[[#This Row],[JAN]:[DEC]])</f>
+        <f>SUM(tblFixed[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="P19" s="24" t="e">
-        <f>AVERAGEIF(tblFixed8[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
+        <f>AVERAGEIF(tblFixed[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q19" s="22" t="e">
-        <f>MEDIAN(tblFixed8[[#This Row],[JAN]:[DEC]])</f>
+        <f>MEDIAN(tblFixed[[#This Row],[JAN]:[DEC]])</f>
         <v>#NUM!</v>
       </c>
       <c r="R19" s="8"/>
@@ -5181,7 +5181,7 @@
       <c r="AJ19" s="4"/>
       <c r="AK19" s="4"/>
     </row>
-    <row r="20" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A20" s="6"/>
       <c r="B20" s="7" t="s">
         <v>29</v>
@@ -5199,15 +5199,15 @@
       <c r="M20" s="22"/>
       <c r="N20" s="22"/>
       <c r="O20" s="22">
-        <f>SUM(tblFixed8[[#This Row],[JAN]:[DEC]])</f>
+        <f>SUM(tblFixed[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="P20" s="24" t="e">
-        <f>AVERAGEIF(tblFixed8[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
+        <f>AVERAGEIF(tblFixed[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q20" s="22" t="e">
-        <f>MEDIAN(tblFixed8[[#This Row],[JAN]:[DEC]])</f>
+        <f>MEDIAN(tblFixed[[#This Row],[JAN]:[DEC]])</f>
         <v>#NUM!</v>
       </c>
       <c r="R20" s="8"/>
@@ -5231,69 +5231,69 @@
       <c r="AJ20" s="4"/>
       <c r="AK20" s="4"/>
     </row>
-    <row r="21" spans="1:37" s="2" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:37" s="2" customFormat="1" ht="22" customHeight="1">
       <c r="A21" s="6"/>
       <c r="B21" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="23">
-        <f>SUBTOTAL(109,tblFixed8[JAN])</f>
+        <f>SUBTOTAL(109,tblFixed[JAN])</f>
         <v>0</v>
       </c>
       <c r="D21" s="23">
-        <f>SUBTOTAL(109,tblFixed8[FEB])</f>
+        <f>SUBTOTAL(109,tblFixed[FEB])</f>
         <v>0</v>
       </c>
       <c r="E21" s="23">
-        <f>SUBTOTAL(109,tblFixed8[MAR])</f>
+        <f>SUBTOTAL(109,tblFixed[MAR])</f>
         <v>0</v>
       </c>
       <c r="F21" s="23">
-        <f>SUBTOTAL(109,tblFixed8[APR])</f>
+        <f>SUBTOTAL(109,tblFixed[APR])</f>
         <v>0</v>
       </c>
       <c r="G21" s="23">
-        <f>SUBTOTAL(109,tblFixed8[MAY])</f>
+        <f>SUBTOTAL(109,tblFixed[MAY])</f>
         <v>0</v>
       </c>
       <c r="H21" s="23">
-        <f>SUBTOTAL(109,tblFixed8[JUN])</f>
+        <f>SUBTOTAL(109,tblFixed[JUN])</f>
         <v>0</v>
       </c>
       <c r="I21" s="23">
-        <f>SUBTOTAL(109,tblFixed8[JUL])</f>
+        <f>SUBTOTAL(109,tblFixed[JUL])</f>
         <v>0</v>
       </c>
       <c r="J21" s="23">
-        <f>SUBTOTAL(109,tblFixed8[AUG])</f>
+        <f>SUBTOTAL(109,tblFixed[AUG])</f>
         <v>0</v>
       </c>
       <c r="K21" s="23">
-        <f>SUBTOTAL(109,tblFixed8[SEP])</f>
+        <f>SUBTOTAL(109,tblFixed[SEP])</f>
         <v>0</v>
       </c>
       <c r="L21" s="23">
-        <f>SUBTOTAL(109,tblFixed8[OCT])</f>
+        <f>SUBTOTAL(109,tblFixed[OCT])</f>
         <v>0</v>
       </c>
       <c r="M21" s="23">
-        <f>SUBTOTAL(109,tblFixed8[NOV])</f>
+        <f>SUBTOTAL(109,tblFixed[NOV])</f>
         <v>0</v>
       </c>
       <c r="N21" s="23">
-        <f>SUBTOTAL(109,tblFixed8[DEC])</f>
+        <f>SUBTOTAL(109,tblFixed[DEC])</f>
         <v>0</v>
       </c>
       <c r="O21" s="23">
-        <f>SUBTOTAL(109,tblFixed8[TOTAL])</f>
+        <f>SUBTOTAL(109,tblFixed[TOTAL])</f>
         <v>0</v>
       </c>
       <c r="P21" s="23" t="e">
-        <f>SUBTOTAL(109,tblFixed8[AVG])</f>
+        <f>SUBTOTAL(109,tblFixed[AVG])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q21" s="23" t="e">
-        <f>SUBTOTAL(109,tblFixed8[MED])</f>
+        <f>SUBTOTAL(109,tblFixed[MED])</f>
         <v>#NUM!</v>
       </c>
       <c r="R21" s="9"/>
@@ -5317,7 +5317,7 @@
       <c r="AJ21" s="4"/>
       <c r="AK21" s="4"/>
     </row>
-    <row r="22" spans="1:37" s="2" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:37" s="2" customFormat="1" ht="35" customHeight="1">
       <c r="A22" s="3"/>
       <c r="B22" s="12" t="s">
         <v>20</v>
@@ -5390,7 +5390,7 @@
       <c r="AJ22" s="4"/>
       <c r="AK22" s="4"/>
     </row>
-    <row r="23" spans="1:37" ht="22.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:37" ht="22.25" customHeight="1">
       <c r="A23" s="11"/>
       <c r="B23" s="7" t="s">
         <v>30</v>
@@ -5408,15 +5408,15 @@
       <c r="M23" s="22"/>
       <c r="N23" s="22"/>
       <c r="O23" s="22">
-        <f>SUM(tblVariable9[[#This Row],[JAN]:[DEC]])</f>
+        <f>SUM(tblVariable[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="P23" s="22" t="e">
-        <f>AVERAGEIF(tblVariable9[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
+        <f>AVERAGEIF(tblVariable[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q23" s="22" t="e">
-        <f>MEDIAN(tblVariable9[[#This Row],[JAN]:[DEC]])</f>
+        <f>MEDIAN(tblVariable[[#This Row],[JAN]:[DEC]])</f>
         <v>#NUM!</v>
       </c>
       <c r="R23" s="8"/>
@@ -5440,7 +5440,7 @@
       <c r="AJ23" s="4"/>
       <c r="AK23" s="4"/>
     </row>
-    <row r="24" spans="1:37" s="14" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:37" s="14" customFormat="1" ht="22.25" customHeight="1">
       <c r="A24" s="6"/>
       <c r="B24" s="7" t="s">
         <v>31</v>
@@ -5458,15 +5458,15 @@
       <c r="M24" s="22"/>
       <c r="N24" s="22"/>
       <c r="O24" s="22">
-        <f>SUM(tblVariable9[[#This Row],[JAN]:[DEC]])</f>
+        <f>SUM(tblVariable[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="P24" s="24" t="e">
-        <f>AVERAGEIF(tblVariable9[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
+        <f>AVERAGEIF(tblVariable[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q24" s="22" t="e">
-        <f>MEDIAN(tblVariable9[[#This Row],[JAN]:[DEC]])</f>
+        <f>MEDIAN(tblVariable[[#This Row],[JAN]:[DEC]])</f>
         <v>#NUM!</v>
       </c>
       <c r="R24" s="8"/>
@@ -5490,7 +5490,7 @@
       <c r="AJ24" s="4"/>
       <c r="AK24" s="4"/>
     </row>
-    <row r="25" spans="1:37" s="2" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:37" s="2" customFormat="1" ht="22" customHeight="1">
       <c r="A25" s="6"/>
       <c r="B25" s="7" t="s">
         <v>32</v>
@@ -5508,15 +5508,15 @@
       <c r="M25" s="22"/>
       <c r="N25" s="22"/>
       <c r="O25" s="22">
-        <f>SUM(tblVariable9[[#This Row],[JAN]:[DEC]])</f>
+        <f>SUM(tblVariable[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="P25" s="24" t="e">
-        <f>AVERAGEIF(tblVariable9[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
+        <f>AVERAGEIF(tblVariable[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q25" s="22" t="e">
-        <f>MEDIAN(tblVariable9[[#This Row],[JAN]:[DEC]])</f>
+        <f>MEDIAN(tblVariable[[#This Row],[JAN]:[DEC]])</f>
         <v>#NUM!</v>
       </c>
       <c r="R25" s="8"/>
@@ -5540,7 +5540,7 @@
       <c r="AJ25" s="4"/>
       <c r="AK25" s="4"/>
     </row>
-    <row r="26" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1">
       <c r="A26" s="6"/>
       <c r="B26" s="7" t="s">
         <v>33</v>
@@ -5558,15 +5558,15 @@
       <c r="M26" s="22"/>
       <c r="N26" s="22"/>
       <c r="O26" s="22">
-        <f>SUM(tblVariable9[[#This Row],[JAN]:[DEC]])</f>
+        <f>SUM(tblVariable[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="P26" s="24" t="e">
-        <f>AVERAGEIF(tblVariable9[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
+        <f>AVERAGEIF(tblVariable[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q26" s="22" t="e">
-        <f>MEDIAN(tblVariable9[[#This Row],[JAN]:[DEC]])</f>
+        <f>MEDIAN(tblVariable[[#This Row],[JAN]:[DEC]])</f>
         <v>#NUM!</v>
       </c>
       <c r="R26" s="8"/>
@@ -5590,7 +5590,7 @@
       <c r="AJ26" s="4"/>
       <c r="AK26" s="4"/>
     </row>
-    <row r="27" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A27" s="6"/>
       <c r="B27" s="7" t="s">
         <v>34</v>
@@ -5608,15 +5608,15 @@
       <c r="M27" s="22"/>
       <c r="N27" s="22"/>
       <c r="O27" s="22">
-        <f>SUM(tblVariable9[[#This Row],[JAN]:[DEC]])</f>
+        <f>SUM(tblVariable[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="P27" s="24" t="e">
-        <f>AVERAGEIF(tblVariable9[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
+        <f>AVERAGEIF(tblVariable[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q27" s="22" t="e">
-        <f>MEDIAN(tblVariable9[[#This Row],[JAN]:[DEC]])</f>
+        <f>MEDIAN(tblVariable[[#This Row],[JAN]:[DEC]])</f>
         <v>#NUM!</v>
       </c>
       <c r="R27" s="8"/>
@@ -5640,7 +5640,7 @@
       <c r="AJ27" s="4"/>
       <c r="AK27" s="4"/>
     </row>
-    <row r="28" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A28" s="6"/>
       <c r="B28" s="7" t="s">
         <v>35</v>
@@ -5658,15 +5658,15 @@
       <c r="M28" s="22"/>
       <c r="N28" s="22"/>
       <c r="O28" s="22">
-        <f>SUM(tblVariable9[[#This Row],[JAN]:[DEC]])</f>
+        <f>SUM(tblVariable[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="P28" s="24" t="e">
-        <f>AVERAGEIF(tblVariable9[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
+        <f>AVERAGEIF(tblVariable[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q28" s="22" t="e">
-        <f>MEDIAN(tblVariable9[[#This Row],[JAN]:[DEC]])</f>
+        <f>MEDIAN(tblVariable[[#This Row],[JAN]:[DEC]])</f>
         <v>#NUM!</v>
       </c>
       <c r="R28" s="8"/>
@@ -5690,7 +5690,7 @@
       <c r="AJ28" s="4"/>
       <c r="AK28" s="4"/>
     </row>
-    <row r="29" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A29" s="6"/>
       <c r="B29" s="7" t="s">
         <v>36</v>
@@ -5708,15 +5708,15 @@
       <c r="M29" s="22"/>
       <c r="N29" s="22"/>
       <c r="O29" s="22">
-        <f>SUM(tblVariable9[[#This Row],[JAN]:[DEC]])</f>
+        <f>SUM(tblVariable[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="P29" s="24" t="e">
-        <f>AVERAGEIF(tblVariable9[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
+        <f>AVERAGEIF(tblVariable[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q29" s="22" t="e">
-        <f>MEDIAN(tblVariable9[[#This Row],[JAN]:[DEC]])</f>
+        <f>MEDIAN(tblVariable[[#This Row],[JAN]:[DEC]])</f>
         <v>#NUM!</v>
       </c>
       <c r="R29" s="8"/>
@@ -5740,7 +5740,7 @@
       <c r="AJ29" s="4"/>
       <c r="AK29" s="4"/>
     </row>
-    <row r="30" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A30" s="6"/>
       <c r="B30" s="7" t="s">
         <v>37</v>
@@ -5758,15 +5758,15 @@
       <c r="M30" s="22"/>
       <c r="N30" s="22"/>
       <c r="O30" s="22">
-        <f>SUM(tblVariable9[[#This Row],[JAN]:[DEC]])</f>
+        <f>SUM(tblVariable[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="P30" s="24" t="e">
-        <f>AVERAGEIF(tblVariable9[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
+        <f>AVERAGEIF(tblVariable[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q30" s="22" t="e">
-        <f>MEDIAN(tblVariable9[[#This Row],[JAN]:[DEC]])</f>
+        <f>MEDIAN(tblVariable[[#This Row],[JAN]:[DEC]])</f>
         <v>#NUM!</v>
       </c>
       <c r="R30" s="8"/>
@@ -5790,7 +5790,7 @@
       <c r="AJ30" s="4"/>
       <c r="AK30" s="4"/>
     </row>
-    <row r="31" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A31" s="6"/>
       <c r="B31" s="7" t="s">
         <v>38</v>
@@ -5808,15 +5808,15 @@
       <c r="M31" s="22"/>
       <c r="N31" s="22"/>
       <c r="O31" s="22">
-        <f>SUM(tblVariable9[[#This Row],[JAN]:[DEC]])</f>
+        <f>SUM(tblVariable[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="P31" s="24" t="e">
-        <f>AVERAGEIF(tblVariable9[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
+        <f>AVERAGEIF(tblVariable[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q31" s="22" t="e">
-        <f>MEDIAN(tblVariable9[[#This Row],[JAN]:[DEC]])</f>
+        <f>MEDIAN(tblVariable[[#This Row],[JAN]:[DEC]])</f>
         <v>#NUM!</v>
       </c>
       <c r="R31" s="8"/>
@@ -5840,7 +5840,7 @@
       <c r="AJ31" s="4"/>
       <c r="AK31" s="4"/>
     </row>
-    <row r="32" spans="1:37" ht="22.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:37" ht="22.25" customHeight="1">
       <c r="A32" s="16"/>
       <c r="B32" s="7" t="s">
         <v>39</v>
@@ -5858,15 +5858,15 @@
       <c r="M32" s="22"/>
       <c r="N32" s="22"/>
       <c r="O32" s="22">
-        <f>SUM(tblVariable9[[#This Row],[JAN]:[DEC]])</f>
+        <f>SUM(tblVariable[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="P32" s="24" t="e">
-        <f>AVERAGEIF(tblVariable9[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
+        <f>AVERAGEIF(tblVariable[[#This Row],[JAN]:[DEC]],"&lt;=0")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q32" s="22" t="e">
-        <f>MEDIAN(tblVariable9[[#This Row],[JAN]:[DEC]])</f>
+        <f>MEDIAN(tblVariable[[#This Row],[JAN]:[DEC]])</f>
         <v>#NUM!</v>
       </c>
       <c r="R32" s="8"/>
@@ -5890,69 +5890,69 @@
       <c r="AJ32" s="4"/>
       <c r="AK32" s="4"/>
     </row>
-    <row r="33" spans="1:37" s="19" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:37" s="19" customFormat="1" ht="22" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C33" s="22">
-        <f>SUBTOTAL(109,tblVariable9[JAN])</f>
+        <f>SUBTOTAL(109,tblVariable[JAN])</f>
         <v>0</v>
       </c>
       <c r="D33" s="22">
-        <f>SUBTOTAL(109,tblVariable9[FEB])</f>
+        <f>SUBTOTAL(109,tblVariable[FEB])</f>
         <v>0</v>
       </c>
       <c r="E33" s="22">
-        <f>SUBTOTAL(109,tblVariable9[MAR])</f>
+        <f>SUBTOTAL(109,tblVariable[MAR])</f>
         <v>0</v>
       </c>
       <c r="F33" s="22">
-        <f>SUBTOTAL(109,tblVariable9[APR])</f>
+        <f>SUBTOTAL(109,tblVariable[APR])</f>
         <v>0</v>
       </c>
       <c r="G33" s="22">
-        <f>SUBTOTAL(109,tblVariable9[MAY])</f>
+        <f>SUBTOTAL(109,tblVariable[MAY])</f>
         <v>0</v>
       </c>
       <c r="H33" s="22">
-        <f>SUBTOTAL(109,tblVariable9[JUN])</f>
+        <f>SUBTOTAL(109,tblVariable[JUN])</f>
         <v>0</v>
       </c>
       <c r="I33" s="22">
-        <f>SUBTOTAL(109,tblVariable9[JUL])</f>
+        <f>SUBTOTAL(109,tblVariable[JUL])</f>
         <v>0</v>
       </c>
       <c r="J33" s="22">
-        <f>SUBTOTAL(109,tblVariable9[AUG])</f>
+        <f>SUBTOTAL(109,tblVariable[AUG])</f>
         <v>0</v>
       </c>
       <c r="K33" s="22">
-        <f>SUBTOTAL(109,tblVariable9[SEP])</f>
+        <f>SUBTOTAL(109,tblVariable[SEP])</f>
         <v>0</v>
       </c>
       <c r="L33" s="22">
-        <f>SUBTOTAL(109,tblVariable9[OCT])</f>
+        <f>SUBTOTAL(109,tblVariable[OCT])</f>
         <v>0</v>
       </c>
       <c r="M33" s="22">
-        <f>SUBTOTAL(109,tblVariable9[NOV])</f>
+        <f>SUBTOTAL(109,tblVariable[NOV])</f>
         <v>0</v>
       </c>
       <c r="N33" s="22">
-        <f>SUBTOTAL(109,tblVariable9[DEC])</f>
+        <f>SUBTOTAL(109,tblVariable[DEC])</f>
         <v>0</v>
       </c>
       <c r="O33" s="22">
-        <f>SUBTOTAL(109,tblVariable9[TOTAL])</f>
+        <f>SUBTOTAL(109,tblVariable[TOTAL])</f>
         <v>0</v>
       </c>
       <c r="P33" s="22" t="e">
-        <f>SUBTOTAL(109,tblVariable9[AVG])</f>
+        <f>SUBTOTAL(109,tblVariable[AVG])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q33" s="22" t="e">
-        <f>SUBTOTAL(109,tblVariable9[MED])</f>
+        <f>SUBTOTAL(109,tblVariable[MED])</f>
         <v>#NUM!</v>
       </c>
       <c r="R33" s="9"/>
@@ -5976,7 +5976,7 @@
       <c r="AJ33" s="4"/>
       <c r="AK33" s="4"/>
     </row>
-    <row r="34" spans="1:37" s="2" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:37" s="2" customFormat="1" ht="35" customHeight="1">
       <c r="A34" s="6"/>
       <c r="B34" s="35" t="s">
         <v>49</v>
@@ -6017,7 +6017,7 @@
       <c r="AJ34" s="4"/>
       <c r="AK34" s="4"/>
     </row>
-    <row r="35" spans="1:37" s="2" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:37" s="2" customFormat="1" ht="35" customHeight="1">
       <c r="A35" s="6"/>
       <c r="B35" s="12" t="s">
         <v>43</v>
@@ -6090,7 +6090,7 @@
       <c r="AJ35" s="4"/>
       <c r="AK35" s="4"/>
     </row>
-    <row r="36" spans="1:37" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:37" ht="22.25" customHeight="1">
       <c r="A36" s="6"/>
       <c r="B36" s="7" t="s">
         <v>44</v>
@@ -6108,15 +6108,15 @@
       <c r="M36" s="22"/>
       <c r="N36" s="22"/>
       <c r="O36" s="22">
-        <f>SUM(tblInvestment11[[#This Row],[JAN]:[DEC]])</f>
+        <f>SUM(tblInvestment[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="P36" s="22" t="e">
-        <f>AVERAGEIF(tblInvestment11[[#This Row],[JAN]:[DEC]],"&gt;=0")</f>
+        <f>AVERAGEIF(tblInvestment[[#This Row],[JAN]:[DEC]],"&gt;=0")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q36" s="22" t="e">
-        <f>MEDIAN(tblInvestment11[[#This Row],[JAN]:[DEC]])</f>
+        <f>MEDIAN(tblInvestment[[#This Row],[JAN]:[DEC]])</f>
         <v>#NUM!</v>
       </c>
       <c r="R36" s="8"/>
@@ -6140,69 +6140,69 @@
       <c r="AJ36" s="4"/>
       <c r="AK36" s="4"/>
     </row>
-    <row r="37" spans="1:37" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:37" s="2" customFormat="1" ht="21" customHeight="1">
       <c r="A37" s="6"/>
       <c r="B37" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C37" s="23">
-        <f>SUBTOTAL(109,tblInvestment11[JAN])</f>
+        <f>SUBTOTAL(109,tblInvestment[JAN])</f>
         <v>0</v>
       </c>
       <c r="D37" s="23">
-        <f>SUBTOTAL(109,tblInvestment11[FEB])</f>
+        <f>SUBTOTAL(109,tblInvestment[FEB])</f>
         <v>0</v>
       </c>
       <c r="E37" s="23">
-        <f>SUBTOTAL(109,tblInvestment11[MAR])</f>
+        <f>SUBTOTAL(109,tblInvestment[MAR])</f>
         <v>0</v>
       </c>
       <c r="F37" s="23">
-        <f>SUBTOTAL(109,tblInvestment11[APR])</f>
+        <f>SUBTOTAL(109,tblInvestment[APR])</f>
         <v>0</v>
       </c>
       <c r="G37" s="23">
-        <f>SUBTOTAL(109,tblInvestment11[MAY])</f>
+        <f>SUBTOTAL(109,tblInvestment[MAY])</f>
         <v>0</v>
       </c>
       <c r="H37" s="23">
-        <f>SUBTOTAL(109,tblInvestment11[JUN])</f>
+        <f>SUBTOTAL(109,tblInvestment[JUN])</f>
         <v>0</v>
       </c>
       <c r="I37" s="23">
-        <f>SUBTOTAL(109,tblInvestment11[JUL])</f>
+        <f>SUBTOTAL(109,tblInvestment[JUL])</f>
         <v>0</v>
       </c>
       <c r="J37" s="23">
-        <f>SUBTOTAL(109,tblInvestment11[AUG])</f>
+        <f>SUBTOTAL(109,tblInvestment[AUG])</f>
         <v>0</v>
       </c>
       <c r="K37" s="23">
-        <f>SUBTOTAL(109,tblInvestment11[SEP])</f>
+        <f>SUBTOTAL(109,tblInvestment[SEP])</f>
         <v>0</v>
       </c>
       <c r="L37" s="23">
-        <f>SUBTOTAL(109,tblInvestment11[OCT])</f>
+        <f>SUBTOTAL(109,tblInvestment[OCT])</f>
         <v>0</v>
       </c>
       <c r="M37" s="23">
-        <f>SUBTOTAL(109,tblInvestment11[NOV])</f>
+        <f>SUBTOTAL(109,tblInvestment[NOV])</f>
         <v>0</v>
       </c>
       <c r="N37" s="23">
-        <f>SUBTOTAL(109,tblInvestment11[DEC])</f>
+        <f>SUBTOTAL(109,tblInvestment[DEC])</f>
         <v>0</v>
       </c>
       <c r="O37" s="23">
-        <f>SUBTOTAL(109,tblInvestment11[TOTAL])</f>
+        <f>SUBTOTAL(109,tblInvestment[TOTAL])</f>
         <v>0</v>
       </c>
       <c r="P37" s="23" t="e">
-        <f>SUBTOTAL(109,tblInvestment11[AVG])</f>
+        <f>SUBTOTAL(109,tblInvestment[AVG])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q37" s="23" t="e">
-        <f>SUBTOTAL(109,tblInvestment11[MED])</f>
+        <f>SUBTOTAL(109,tblInvestment[MED])</f>
         <v>#NUM!</v>
       </c>
       <c r="R37" s="9"/>
@@ -6226,10 +6226,10 @@
       <c r="AJ37" s="4"/>
       <c r="AK37" s="4"/>
     </row>
-    <row r="38" spans="1:37" s="37" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:37" s="37" customFormat="1" ht="20" customHeight="1">
       <c r="A38" s="39"/>
     </row>
-    <row r="39" spans="1:37" ht="34" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:37" ht="34" customHeight="1">
       <c r="A39" s="6"/>
       <c r="B39" s="40" t="s">
         <v>17</v>
@@ -6302,69 +6302,69 @@
       <c r="AJ39" s="4"/>
       <c r="AK39" s="4"/>
     </row>
-    <row r="40" spans="1:37" s="14" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:37" s="14" customFormat="1" ht="22" customHeight="1">
       <c r="A40" s="6"/>
       <c r="B40" s="31" t="s">
         <v>18</v>
       </c>
       <c r="C40" s="28">
-        <f>SUM(tblVariable9[[#Totals],[JAN]],tblFixed8[[#Totals],[JAN]])</f>
+        <f>SUM(tblVariable[[#Totals],[JAN]],tblFixed[[#Totals],[JAN]])</f>
         <v>0</v>
       </c>
       <c r="D40" s="30">
-        <f>SUM(tblVariable9[[#Totals],[FEB]],tblFixed8[[#Totals],[FEB]])</f>
+        <f>SUM(tblVariable[[#Totals],[FEB]],tblFixed[[#Totals],[FEB]])</f>
         <v>0</v>
       </c>
       <c r="E40" s="28">
-        <f>SUM(tblVariable9[[#Totals],[MAR]],tblFixed8[[#Totals],[MAR]])</f>
+        <f>SUM(tblVariable[[#Totals],[MAR]],tblFixed[[#Totals],[MAR]])</f>
         <v>0</v>
       </c>
       <c r="F40" s="30">
-        <f>SUM(tblVariable9[[#Totals],[APR]],tblFixed8[[#Totals],[APR]])</f>
+        <f>SUM(tblVariable[[#Totals],[APR]],tblFixed[[#Totals],[APR]])</f>
         <v>0</v>
       </c>
       <c r="G40" s="28">
-        <f>SUM(tblVariable9[[#Totals],[MAY]],tblFixed8[[#Totals],[MAY]])</f>
+        <f>SUM(tblVariable[[#Totals],[MAY]],tblFixed[[#Totals],[MAY]])</f>
         <v>0</v>
       </c>
       <c r="H40" s="30">
-        <f>SUM(tblVariable9[[#Totals],[JUN]],tblFixed8[[#Totals],[JUN]])</f>
+        <f>SUM(tblVariable[[#Totals],[JUN]],tblFixed[[#Totals],[JUN]])</f>
         <v>0</v>
       </c>
       <c r="I40" s="25">
-        <f>SUM(tblVariable9[[#Totals],[JUL]],tblFixed8[[#Totals],[JUL]])</f>
+        <f>SUM(tblVariable[[#Totals],[JUL]],tblFixed[[#Totals],[JUL]])</f>
         <v>0</v>
       </c>
       <c r="J40" s="30">
-        <f>SUM(tblVariable9[[#Totals],[AUG]],tblFixed8[[#Totals],[AUG]])</f>
+        <f>SUM(tblVariable[[#Totals],[AUG]],tblFixed[[#Totals],[AUG]])</f>
         <v>0</v>
       </c>
       <c r="K40" s="25">
-        <f>SUM(tblVariable9[[#Totals],[SEP]],tblFixed8[[#Totals],[SEP]])</f>
+        <f>SUM(tblVariable[[#Totals],[SEP]],tblFixed[[#Totals],[SEP]])</f>
         <v>0</v>
       </c>
       <c r="L40" s="30">
-        <f>SUM(tblVariable9[[#Totals],[OCT]],tblFixed8[[#Totals],[OCT]])</f>
+        <f>SUM(tblVariable[[#Totals],[OCT]],tblFixed[[#Totals],[OCT]])</f>
         <v>0</v>
       </c>
       <c r="M40" s="25">
-        <f>SUM(tblVariable9[[#Totals],[NOV]],tblFixed8[[#Totals],[NOV]])</f>
+        <f>SUM(tblVariable[[#Totals],[NOV]],tblFixed[[#Totals],[NOV]])</f>
         <v>0</v>
       </c>
       <c r="N40" s="30">
-        <f>SUM(tblVariable9[[#Totals],[DEC]],tblFixed8[[#Totals],[DEC]])</f>
+        <f>SUM(tblVariable[[#Totals],[DEC]],tblFixed[[#Totals],[DEC]])</f>
         <v>0</v>
       </c>
       <c r="O40" s="25">
-        <f>SUM(tblTotals510[[#This Row],[JAN]:[DEC]])</f>
+        <f>SUM(tblTotals[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="P40" s="30" t="e">
-        <f>AVERAGEIF(tblTotals510[[#This Row],[JAN]:[DEC]],"&lt;&gt;0")</f>
+        <f>AVERAGEIF(tblTotals[[#This Row],[JAN]:[DEC]],"&lt;&gt;0")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q40" s="25">
-        <f>MEDIAN(tblTotals510[[#This Row],[JAN]:[DEC]])</f>
+        <f>MEDIAN(tblTotals[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="R40" s="32"/>
@@ -6388,69 +6388,69 @@
       <c r="AJ40" s="4"/>
       <c r="AK40" s="4"/>
     </row>
-    <row r="41" spans="1:37" s="14" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:37" s="14" customFormat="1" ht="23" customHeight="1">
       <c r="A41" s="6"/>
       <c r="B41" s="31" t="s">
         <v>48</v>
       </c>
       <c r="C41" s="28">
-        <f>SUM(tblIncome7[[#Totals],[JAN]])</f>
+        <f>SUM(tblIncome[[#Totals],[JAN]])</f>
         <v>0</v>
       </c>
       <c r="D41" s="30">
-        <f>SUM(tblIncome7[[#Totals],[FEB]])</f>
+        <f>SUM(tblIncome[[#Totals],[FEB]])</f>
         <v>0</v>
       </c>
       <c r="E41" s="28">
-        <f>SUM(tblIncome7[[#Totals],[MAR]])</f>
+        <f>SUM(tblIncome[[#Totals],[MAR]])</f>
         <v>0</v>
       </c>
       <c r="F41" s="30">
-        <f>SUM(tblIncome7[[#Totals],[APR]])</f>
+        <f>SUM(tblIncome[[#Totals],[APR]])</f>
         <v>0</v>
       </c>
       <c r="G41" s="28">
-        <f>SUM(tblIncome7[[#Totals],[MAY]])</f>
+        <f>SUM(tblIncome[[#Totals],[MAY]])</f>
         <v>0</v>
       </c>
       <c r="H41" s="30">
-        <f>SUM(tblIncome7[[#Totals],[JUN]])</f>
+        <f>SUM(tblIncome[[#Totals],[JUN]])</f>
         <v>0</v>
       </c>
       <c r="I41" s="25">
-        <f>SUM(tblIncome7[[#Totals],[JUL]])</f>
+        <f>SUM(tblIncome[[#Totals],[JUL]])</f>
         <v>0</v>
       </c>
       <c r="J41" s="30">
-        <f>SUM(tblIncome7[[#Totals],[AUG]])</f>
+        <f>SUM(tblIncome[[#Totals],[AUG]])</f>
         <v>0</v>
       </c>
       <c r="K41" s="25">
-        <f>SUM(tblIncome7[[#Totals],[SEP]])</f>
+        <f>SUM(tblIncome[[#Totals],[SEP]])</f>
         <v>0</v>
       </c>
       <c r="L41" s="30">
-        <f>SUM(tblIncome7[[#Totals],[OCT]])</f>
+        <f>SUM(tblIncome[[#Totals],[OCT]])</f>
         <v>0</v>
       </c>
       <c r="M41" s="25">
-        <f>SUM(tblIncome7[[#Totals],[NOV]])</f>
+        <f>SUM(tblIncome[[#Totals],[NOV]])</f>
         <v>0</v>
       </c>
       <c r="N41" s="30">
-        <f>SUM(tblIncome7[[#Totals],[DEC]])</f>
+        <f>SUM(tblIncome[[#Totals],[DEC]])</f>
         <v>0</v>
       </c>
       <c r="O41" s="25">
-        <f>SUM(tblTotals510[[#This Row],[JAN]:[DEC]])</f>
+        <f>SUM(tblTotals[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="P41" s="30" t="e">
-        <f>AVERAGEIF(tblTotals510[[#This Row],[JAN]:[DEC]],"&lt;&gt;0")</f>
+        <f>AVERAGEIF(tblTotals[[#This Row],[JAN]:[DEC]],"&lt;&gt;0")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q41" s="25">
-        <f>MEDIAN(tblTotals510[[#This Row],[JAN]:[DEC]])</f>
+        <f>MEDIAN(tblTotals[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="R41" s="32"/>
@@ -6474,7 +6474,7 @@
       <c r="AJ41" s="4"/>
       <c r="AK41" s="4"/>
     </row>
-    <row r="42" spans="1:37" s="2" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:37" s="2" customFormat="1" ht="7" customHeight="1">
       <c r="A42" s="6"/>
       <c r="B42" s="33"/>
       <c r="C42" s="29"/>
@@ -6513,69 +6513,69 @@
       <c r="AJ42" s="4"/>
       <c r="AK42" s="4"/>
     </row>
-    <row r="43" spans="1:37" s="2" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:37" s="2" customFormat="1" ht="22" customHeight="1">
       <c r="A43" s="6"/>
       <c r="B43" s="31" t="s">
         <v>51</v>
       </c>
       <c r="C43" s="28">
-        <f>SUM(C40,C41,tblInvestment11[[#Totals],[JAN]])</f>
+        <f>SUM(C40,C41,tblInvestment[[#Totals],[JAN]])</f>
         <v>0</v>
       </c>
       <c r="D43" s="30">
-        <f>SUM(D40,D41,tblInvestment11[[#Totals],[FEB]])</f>
+        <f>SUM(D40,D41,tblInvestment[[#Totals],[FEB]])</f>
         <v>0</v>
       </c>
       <c r="E43" s="28">
-        <f>SUM(E40,E41,tblInvestment11[[#Totals],[MAR]])</f>
+        <f>SUM(E40,E41,tblInvestment[[#Totals],[MAR]])</f>
         <v>0</v>
       </c>
       <c r="F43" s="30">
-        <f>SUM(F40,F41,tblInvestment11[[#Totals],[APR]])</f>
+        <f>SUM(F40,F41,tblInvestment[[#Totals],[APR]])</f>
         <v>0</v>
       </c>
       <c r="G43" s="28">
-        <f>SUM(G40,G41,tblInvestment11[[#Totals],[MAY]])</f>
+        <f>SUM(G40,G41,tblInvestment[[#Totals],[MAY]])</f>
         <v>0</v>
       </c>
       <c r="H43" s="30">
-        <f>SUM(H40,H41,tblInvestment11[[#Totals],[JUN]])</f>
+        <f>SUM(H40,H41,tblInvestment[[#Totals],[JUN]])</f>
         <v>0</v>
       </c>
       <c r="I43" s="25">
-        <f>SUM(I40,I41,tblInvestment11[[#Totals],[JUL]])</f>
+        <f>SUM(I40,I41,tblInvestment[[#Totals],[JUL]])</f>
         <v>0</v>
       </c>
       <c r="J43" s="30">
-        <f>SUM(J40,J41,tblInvestment11[[#Totals],[AUG]])</f>
+        <f>SUM(J40,J41,tblInvestment[[#Totals],[AUG]])</f>
         <v>0</v>
       </c>
       <c r="K43" s="25">
-        <f>SUM(K40,K41,tblInvestment11[[#Totals],[SEP]])</f>
+        <f>SUM(K40,K41,tblInvestment[[#Totals],[SEP]])</f>
         <v>0</v>
       </c>
       <c r="L43" s="30">
-        <f>SUM(L40,L41,tblInvestment11[[#Totals],[OCT]])</f>
+        <f>SUM(L40,L41,tblInvestment[[#Totals],[OCT]])</f>
         <v>0</v>
       </c>
       <c r="M43" s="25">
-        <f>SUM(M40,M41,tblInvestment11[[#Totals],[NOV]])</f>
+        <f>SUM(M40,M41,tblInvestment[[#Totals],[NOV]])</f>
         <v>0</v>
       </c>
       <c r="N43" s="30">
-        <f>SUM(N40,N41,tblInvestment11[[#Totals],[DEC]])</f>
+        <f>SUM(N40,N41,tblInvestment[[#Totals],[DEC]])</f>
         <v>0</v>
       </c>
       <c r="O43" s="25">
-        <f>SUM(tblTotals510[[#This Row],[JAN]:[DEC]])</f>
+        <f>SUM(tblTotals[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="P43" s="30" t="e">
-        <f>AVERAGEIF(tblTotals510[[#This Row],[JAN]:[DEC]], "&lt;&gt;0")</f>
+        <f>AVERAGEIF(tblTotals[[#This Row],[JAN]:[DEC]], "&lt;&gt;0")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q43" s="25">
-        <f>MEDIAN(tblTotals510[[#This Row],[JAN]:[DEC]])</f>
+        <f>MEDIAN(tblTotals[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="R43" s="32"/>
@@ -6599,7 +6599,7 @@
       <c r="AJ43" s="4"/>
       <c r="AK43" s="4"/>
     </row>
-    <row r="44" spans="1:37" s="37" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:37" s="37" customFormat="1" ht="22.25" customHeight="1">
       <c r="B44" s="31" t="s">
         <v>50</v>
       </c>
@@ -6652,20 +6652,20 @@
         <v>0</v>
       </c>
       <c r="O44" s="25">
-        <f>SUM(tblTotals510[[#This Row],[JAN]:[DEC]])</f>
+        <f>SUM(tblTotals[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="P44" s="30" t="e">
-        <f>AVERAGEIF(tblTotals510[[#This Row],[JAN]:[DEC]], "&lt;&gt;0")</f>
+        <f>AVERAGEIF(tblTotals[[#This Row],[JAN]:[DEC]], "&lt;&gt;0")</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q44" s="25">
-        <f>MEDIAN(tblTotals510[[#This Row],[JAN]:[DEC]])</f>
+        <f>MEDIAN(tblTotals[[#This Row],[JAN]:[DEC]])</f>
         <v>0</v>
       </c>
       <c r="R44" s="32"/>
     </row>
-    <row r="45" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A45" s="4"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -6704,7 +6704,7 @@
       <c r="AJ45" s="4"/>
       <c r="AK45" s="4"/>
     </row>
-    <row r="46" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -6743,7 +6743,7 @@
       <c r="AJ46" s="4"/>
       <c r="AK46" s="4"/>
     </row>
-    <row r="47" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -6782,7 +6782,7 @@
       <c r="AJ47" s="4"/>
       <c r="AK47" s="4"/>
     </row>
-    <row r="48" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -6821,7 +6821,7 @@
       <c r="AJ48" s="4"/>
       <c r="AK48" s="4"/>
     </row>
-    <row r="49" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A49" s="4"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -6860,7 +6860,7 @@
       <c r="AJ49" s="4"/>
       <c r="AK49" s="4"/>
     </row>
-    <row r="50" spans="1:37" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:37" ht="22.25" customHeight="1">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -6901,7 +6901,7 @@
       <c r="AJ50" s="4"/>
       <c r="AK50" s="4"/>
     </row>
-    <row r="51" spans="1:37" s="14" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:37" s="14" customFormat="1" ht="22.25" customHeight="1">
       <c r="A51" s="6"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -6940,7 +6940,7 @@
       <c r="AJ51" s="4"/>
       <c r="AK51" s="4"/>
     </row>
-    <row r="52" spans="1:37" s="2" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:37" s="2" customFormat="1" ht="22" customHeight="1">
       <c r="A52" s="6"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -6979,7 +6979,7 @@
       <c r="AJ52" s="4"/>
       <c r="AK52" s="4"/>
     </row>
-    <row r="53" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1">
       <c r="A53" s="4"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -7018,7 +7018,7 @@
       <c r="AJ53" s="4"/>
       <c r="AK53" s="4"/>
     </row>
-    <row r="54" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A54" s="4"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -7057,7 +7057,7 @@
       <c r="AJ54" s="4"/>
       <c r="AK54" s="4"/>
     </row>
-    <row r="55" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -7096,7 +7096,7 @@
       <c r="AJ55" s="4"/>
       <c r="AK55" s="4"/>
     </row>
-    <row r="56" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -7135,7 +7135,7 @@
       <c r="AJ56" s="4"/>
       <c r="AK56" s="4"/>
     </row>
-    <row r="57" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -7174,7 +7174,7 @@
       <c r="AJ57" s="4"/>
       <c r="AK57" s="4"/>
     </row>
-    <row r="58" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A58" s="6"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -7213,7 +7213,7 @@
       <c r="AJ58" s="4"/>
       <c r="AK58" s="4"/>
     </row>
-    <row r="59" spans="1:37" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:37" ht="22.25" customHeight="1">
       <c r="A59" s="6"/>
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
@@ -7249,7 +7249,7 @@
       <c r="AJ59" s="4"/>
       <c r="AK59" s="4"/>
     </row>
-    <row r="60" spans="1:37" s="14" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:37" s="14" customFormat="1" ht="22.25" customHeight="1">
       <c r="A60" s="6"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -7288,7 +7288,7 @@
       <c r="AJ60" s="4"/>
       <c r="AK60" s="4"/>
     </row>
-    <row r="61" spans="1:37" s="2" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:37" s="2" customFormat="1" ht="22" customHeight="1">
       <c r="A61" s="4"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -7327,7 +7327,7 @@
       <c r="AJ61" s="4"/>
       <c r="AK61" s="4"/>
     </row>
-    <row r="62" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1">
       <c r="A62" s="4"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -7366,7 +7366,7 @@
       <c r="AJ62" s="4"/>
       <c r="AK62" s="4"/>
     </row>
-    <row r="63" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -7405,7 +7405,7 @@
       <c r="AJ63" s="4"/>
       <c r="AK63" s="4"/>
     </row>
-    <row r="64" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -7444,7 +7444,7 @@
       <c r="AJ64" s="4"/>
       <c r="AK64" s="4"/>
     </row>
-    <row r="65" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -7483,7 +7483,7 @@
       <c r="AJ65" s="4"/>
       <c r="AK65" s="4"/>
     </row>
-    <row r="66" spans="1:37" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:37" ht="22.25" customHeight="1">
       <c r="A66" s="4"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
@@ -7522,7 +7522,7 @@
       <c r="AJ66" s="4"/>
       <c r="AK66" s="4"/>
     </row>
-    <row r="67" spans="1:37" s="14" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:37" s="14" customFormat="1" ht="22.25" customHeight="1">
       <c r="A67" s="6"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -7561,7 +7561,7 @@
       <c r="AJ67" s="4"/>
       <c r="AK67" s="4"/>
     </row>
-    <row r="68" spans="1:37" s="2" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:37" s="2" customFormat="1" ht="22" customHeight="1">
       <c r="A68" s="6"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -7600,7 +7600,7 @@
       <c r="AJ68" s="4"/>
       <c r="AK68" s="4"/>
     </row>
-    <row r="69" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1">
       <c r="A69" s="6"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -7639,7 +7639,7 @@
       <c r="AJ69" s="4"/>
       <c r="AK69" s="4"/>
     </row>
-    <row r="70" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A70" s="4"/>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
@@ -7678,7 +7678,7 @@
       <c r="AJ70" s="4"/>
       <c r="AK70" s="4"/>
     </row>
-    <row r="71" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A71" s="4"/>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
@@ -7717,7 +7717,7 @@
       <c r="AJ71" s="4"/>
       <c r="AK71" s="4"/>
     </row>
-    <row r="72" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -7756,7 +7756,7 @@
       <c r="AJ72" s="4"/>
       <c r="AK72" s="4"/>
     </row>
-    <row r="73" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -7795,7 +7795,7 @@
       <c r="AJ73" s="4"/>
       <c r="AK73" s="4"/>
     </row>
-    <row r="74" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -7834,7 +7834,7 @@
       <c r="AJ74" s="4"/>
       <c r="AK74" s="4"/>
     </row>
-    <row r="75" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A75" s="6"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -7873,7 +7873,7 @@
       <c r="AJ75" s="4"/>
       <c r="AK75" s="4"/>
     </row>
-    <row r="76" spans="1:37" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:37" ht="22.25" customHeight="1">
       <c r="A76" s="6"/>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
@@ -7909,7 +7909,7 @@
       <c r="AJ76" s="4"/>
       <c r="AK76" s="4"/>
     </row>
-    <row r="77" spans="1:37" s="14" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:37" s="14" customFormat="1" ht="22.25" customHeight="1">
       <c r="A77" s="6"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -7948,7 +7948,7 @@
       <c r="AJ77" s="4"/>
       <c r="AK77" s="4"/>
     </row>
-    <row r="78" spans="1:37" s="2" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:37" s="2" customFormat="1" ht="22" customHeight="1">
       <c r="A78" s="4"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
@@ -7987,7 +7987,7 @@
       <c r="AJ78" s="4"/>
       <c r="AK78" s="4"/>
     </row>
-    <row r="79" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1">
       <c r="A79" s="4"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -8026,7 +8026,7 @@
       <c r="AJ79" s="4"/>
       <c r="AK79" s="4"/>
     </row>
-    <row r="80" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -8065,7 +8065,7 @@
       <c r="AJ80" s="4"/>
       <c r="AK80" s="4"/>
     </row>
-    <row r="81" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -8104,7 +8104,7 @@
       <c r="AJ81" s="4"/>
       <c r="AK81" s="4"/>
     </row>
-    <row r="82" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -8143,7 +8143,7 @@
       <c r="AJ82" s="4"/>
       <c r="AK82" s="4"/>
     </row>
-    <row r="83" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A83" s="4"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -8182,7 +8182,7 @@
       <c r="AJ83" s="4"/>
       <c r="AK83" s="4"/>
     </row>
-    <row r="84" spans="1:37" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:37" ht="22.25" customHeight="1">
       <c r="A84" s="6"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -8221,7 +8221,7 @@
       <c r="AJ84" s="4"/>
       <c r="AK84" s="4"/>
     </row>
-    <row r="85" spans="1:37" s="14" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:37" s="14" customFormat="1" ht="22.25" customHeight="1">
       <c r="A85" s="6"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -8260,7 +8260,7 @@
       <c r="AJ85" s="4"/>
       <c r="AK85" s="4"/>
     </row>
-    <row r="86" spans="1:37" s="2" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:37" s="2" customFormat="1" ht="22" customHeight="1">
       <c r="A86" s="6"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -8299,7 +8299,7 @@
       <c r="AJ86" s="4"/>
       <c r="AK86" s="4"/>
     </row>
-    <row r="87" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1">
       <c r="A87" s="4"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -8338,7 +8338,7 @@
       <c r="AJ87" s="4"/>
       <c r="AK87" s="4"/>
     </row>
-    <row r="88" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A88" s="4"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -8377,7 +8377,7 @@
       <c r="AJ88" s="4"/>
       <c r="AK88" s="4"/>
     </row>
-    <row r="89" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -8416,7 +8416,7 @@
       <c r="AJ89" s="4"/>
       <c r="AK89" s="4"/>
     </row>
-    <row r="90" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -8455,7 +8455,7 @@
       <c r="AJ90" s="4"/>
       <c r="AK90" s="4"/>
     </row>
-    <row r="91" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -8494,7 +8494,7 @@
       <c r="AJ91" s="4"/>
       <c r="AK91" s="4"/>
     </row>
-    <row r="92" spans="1:37" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:37" ht="22.25" customHeight="1">
       <c r="A92" s="6"/>
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
@@ -8530,7 +8530,7 @@
       <c r="AJ92" s="4"/>
       <c r="AK92" s="4"/>
     </row>
-    <row r="93" spans="1:37" s="14" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:37" s="14" customFormat="1" ht="22.25" customHeight="1">
       <c r="A93" s="6"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -8569,7 +8569,7 @@
       <c r="AJ93" s="4"/>
       <c r="AK93" s="4"/>
     </row>
-    <row r="94" spans="1:37" s="2" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:37" s="2" customFormat="1" ht="22" customHeight="1">
       <c r="A94" s="6"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -8608,7 +8608,7 @@
       <c r="AJ94" s="4"/>
       <c r="AK94" s="4"/>
     </row>
-    <row r="95" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1">
       <c r="A95" s="4"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -8647,7 +8647,7 @@
       <c r="AJ95" s="4"/>
       <c r="AK95" s="4"/>
     </row>
-    <row r="96" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A96" s="4"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -8686,7 +8686,7 @@
       <c r="AJ96" s="4"/>
       <c r="AK96" s="4"/>
     </row>
-    <row r="97" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -8725,7 +8725,7 @@
       <c r="AJ97" s="4"/>
       <c r="AK97" s="4"/>
     </row>
-    <row r="98" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -8764,7 +8764,7 @@
       <c r="AJ98" s="4"/>
       <c r="AK98" s="4"/>
     </row>
-    <row r="99" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:37" s="2" customFormat="1" ht="22.25" customHeight="1">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -8803,7 +8803,7 @@
       <c r="AJ99" s="4"/>
       <c r="AK99" s="4"/>
     </row>
-    <row r="100" spans="1:37" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:37" ht="22.25" customHeight="1">
       <c r="A100" s="4"/>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
@@ -8842,7 +8842,7 @@
       <c r="AJ100" s="4"/>
       <c r="AK100" s="4"/>
     </row>
-    <row r="101" spans="1:37" s="15" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:37" s="15" customFormat="1" ht="22.25" customHeight="1">
       <c r="A101" s="6"/>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
@@ -8881,7 +8881,7 @@
       <c r="AJ101" s="4"/>
       <c r="AK101" s="4"/>
     </row>
-    <row r="102" spans="1:37" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:37" ht="22" customHeight="1">
       <c r="A102" s="6"/>
       <c r="C102" s="4"/>
       <c r="D102" s="4"/>
@@ -8917,7 +8917,7 @@
       <c r="AJ102" s="4"/>
       <c r="AK102" s="4"/>
     </row>
-    <row r="103" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:37" ht="30" customHeight="1">
       <c r="A103" s="6"/>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
@@ -8956,7 +8956,7 @@
       <c r="AJ103" s="4"/>
       <c r="AK103" s="4"/>
     </row>
-    <row r="104" spans="1:37" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:37" ht="22" customHeight="1">
       <c r="A104" s="4"/>
       <c r="B104" s="6"/>
       <c r="C104" s="6"/>
@@ -8995,7 +8995,7 @@
       <c r="AJ104" s="4"/>
       <c r="AK104" s="4"/>
     </row>
-    <row r="105" spans="1:37" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:37" ht="22" customHeight="1">
       <c r="A105" s="4"/>
       <c r="B105" s="6"/>
       <c r="C105" s="6"/>
@@ -9034,7 +9034,7 @@
       <c r="AJ105" s="4"/>
       <c r="AK105" s="4"/>
     </row>
-    <row r="106" spans="1:37" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:37" ht="22" customHeight="1">
       <c r="A106" s="4"/>
       <c r="C106" s="4"/>
       <c r="D106" s="4"/>
@@ -9070,7 +9070,7 @@
       <c r="AJ106" s="4"/>
       <c r="AK106" s="4"/>
     </row>
-    <row r="107" spans="1:37" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:37" ht="22" customHeight="1">
       <c r="A107" s="4"/>
       <c r="C107" s="4"/>
       <c r="D107" s="4"/>
@@ -9106,7 +9106,7 @@
       <c r="AJ107" s="4"/>
       <c r="AK107" s="4"/>
     </row>
-    <row r="108" spans="1:37" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:37" ht="22" customHeight="1">
       <c r="A108" s="4"/>
       <c r="C108" s="4"/>
       <c r="D108" s="4"/>
@@ -9142,7 +9142,7 @@
       <c r="AJ108" s="4"/>
       <c r="AK108" s="4"/>
     </row>
-    <row r="109" spans="1:37" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:37" ht="22" customHeight="1">
       <c r="A109" s="6"/>
       <c r="C109" s="4"/>
       <c r="D109" s="4"/>
@@ -9178,7 +9178,7 @@
       <c r="AJ109" s="4"/>
       <c r="AK109" s="4"/>
     </row>
-    <row r="110" spans="1:37" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:37" ht="22" customHeight="1">
       <c r="A110" s="6"/>
       <c r="C110" s="4"/>
       <c r="D110" s="4"/>
@@ -9214,7 +9214,7 @@
       <c r="AJ110" s="4"/>
       <c r="AK110" s="4"/>
     </row>
-    <row r="111" spans="1:37" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:37" ht="22" customHeight="1">
       <c r="A111" s="6"/>
       <c r="C111" s="4"/>
       <c r="D111" s="4"/>
@@ -9250,7 +9250,7 @@
       <c r="AJ111" s="4"/>
       <c r="AK111" s="4"/>
     </row>
-    <row r="112" spans="1:37" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:37" ht="22" customHeight="1">
       <c r="A112" s="4"/>
       <c r="B112" s="6"/>
       <c r="C112" s="6"/>
@@ -9289,7 +9289,7 @@
       <c r="AJ112" s="4"/>
       <c r="AK112" s="4"/>
     </row>
-    <row r="113" spans="1:37" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:37" ht="22" customHeight="1">
       <c r="A113" s="4"/>
       <c r="B113" s="6"/>
       <c r="C113" s="6"/>
@@ -9328,7 +9328,7 @@
       <c r="AJ113" s="4"/>
       <c r="AK113" s="4"/>
     </row>
-    <row r="114" spans="1:37" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:37" ht="22" customHeight="1">
       <c r="A114" s="4"/>
       <c r="C114" s="4"/>
       <c r="D114" s="4"/>
@@ -9366,7 +9366,7 @@
       <c r="AJ114" s="4"/>
       <c r="AK114" s="4"/>
     </row>
-    <row r="115" spans="1:37" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:37" ht="22" customHeight="1">
       <c r="A115" s="4"/>
       <c r="C115" s="4"/>
       <c r="D115" s="4"/>
@@ -9404,7 +9404,7 @@
       <c r="AJ115" s="4"/>
       <c r="AK115" s="4"/>
     </row>
-    <row r="116" spans="1:37" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:37" ht="22" customHeight="1">
       <c r="A116" s="4"/>
       <c r="C116" s="4"/>
       <c r="D116" s="4"/>
@@ -9442,7 +9442,7 @@
       <c r="AJ116" s="4"/>
       <c r="AK116" s="4"/>
     </row>
-    <row r="117" spans="1:37" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:37" ht="22" customHeight="1">
       <c r="A117" s="4"/>
       <c r="B117" s="6"/>
       <c r="C117" s="6"/>
@@ -9481,7 +9481,7 @@
       <c r="AJ117" s="4"/>
       <c r="AK117" s="4"/>
     </row>
-    <row r="118" spans="1:37" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:37" ht="22" customHeight="1">
       <c r="A118" s="6"/>
       <c r="B118" s="6"/>
       <c r="C118" s="6"/>
@@ -9520,7 +9520,7 @@
       <c r="AJ118" s="4"/>
       <c r="AK118" s="4"/>
     </row>
-    <row r="119" spans="1:37" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:37" ht="22" customHeight="1">
       <c r="A119" s="6"/>
       <c r="C119" s="4"/>
       <c r="D119" s="4"/>
@@ -9556,7 +9556,7 @@
       <c r="AJ119" s="4"/>
       <c r="AK119" s="4"/>
     </row>
-    <row r="120" spans="1:37" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:37" ht="22" customHeight="1">
       <c r="A120" s="6"/>
       <c r="B120" s="6"/>
       <c r="C120" s="6"/>
@@ -9595,7 +9595,7 @@
       <c r="AJ120" s="4"/>
       <c r="AK120" s="4"/>
     </row>
-    <row r="121" spans="1:37" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:37" ht="22" customHeight="1">
       <c r="A121" s="4"/>
       <c r="B121" s="6"/>
       <c r="C121" s="6"/>
@@ -9634,7 +9634,7 @@
       <c r="AJ121" s="4"/>
       <c r="AK121" s="4"/>
     </row>
-    <row r="122" spans="1:37" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:37" ht="22" customHeight="1">
       <c r="A122" s="4"/>
       <c r="B122" s="6"/>
       <c r="C122" s="6"/>
@@ -9673,7 +9673,7 @@
       <c r="AJ122" s="4"/>
       <c r="AK122" s="4"/>
     </row>
-    <row r="123" spans="1:37" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:37" ht="22" customHeight="1">
       <c r="A123" s="4"/>
       <c r="C123" s="4"/>
       <c r="D123" s="4"/>
@@ -9709,7 +9709,7 @@
       <c r="AJ123" s="4"/>
       <c r="AK123" s="4"/>
     </row>
-    <row r="124" spans="1:37" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:37" ht="22" customHeight="1">
       <c r="A124" s="4"/>
       <c r="C124" s="4"/>
       <c r="D124" s="4"/>
@@ -9745,7 +9745,7 @@
       <c r="AJ124" s="4"/>
       <c r="AK124" s="4"/>
     </row>
-    <row r="125" spans="1:37" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:37" ht="22" customHeight="1">
       <c r="A125" s="4"/>
       <c r="C125" s="4"/>
       <c r="D125" s="4"/>
@@ -9781,7 +9781,7 @@
       <c r="AJ125" s="4"/>
       <c r="AK125" s="4"/>
     </row>
-    <row r="126" spans="1:37" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:37" ht="22" customHeight="1">
       <c r="C126" s="4"/>
       <c r="D126" s="4"/>
       <c r="E126" s="4"/>
@@ -9797,7 +9797,7 @@
       <c r="O126" s="4"/>
       <c r="R126" s="4"/>
     </row>
-    <row r="127" spans="1:37" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:37" ht="22" customHeight="1">
       <c r="C127" s="4"/>
       <c r="D127" s="4"/>
       <c r="E127" s="4"/>
@@ -9813,7 +9813,7 @@
       <c r="O127" s="4"/>
       <c r="R127" s="4"/>
     </row>
-    <row r="128" spans="1:37" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:37" ht="22" customHeight="1">
       <c r="C128" s="4"/>
       <c r="D128" s="4"/>
       <c r="E128" s="4"/>
@@ -9848,7 +9848,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
       <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1" xr2:uid="{684D059B-A148-7B4D-9E6A-6A758AEBB88C}">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1" xr2:uid="{A51D215C-6A0C-D443-9A45-6910023EF5F6}">
           <x14:colorSeries theme="4" tint="-0.499984740745262"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -9859,40 +9859,104 @@
           <x14:colorLow theme="4"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>Sheet1!C21:N21</xm:f>
-              <xm:sqref>R21</xm:sqref>
+              <xm:f>Sheet1!C6:N6</xm:f>
+              <xm:sqref>R6</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!C7:N7</xm:f>
+              <xm:sqref>R7</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!C8:N8</xm:f>
+              <xm:sqref>R8</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!C9:N9</xm:f>
+              <xm:sqref>R9</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" markers="1" high="1" low="1" xr2:uid="{3489094E-86F0-554F-8EA5-9E9DAEA9CAA8}">
-          <x14:colorSeries theme="0"/>
-          <x14:colorNegative theme="6"/>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1" xr2:uid="{382C768D-DF9D-8946-BAD3-24209AB66791}">
+          <x14:colorSeries theme="4" tint="-0.499984740745262"/>
+          <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers theme="0"/>
-          <x14:colorFirst theme="5" tint="0.39997558519241921"/>
-          <x14:colorLast theme="5" tint="0.39997558519241921"/>
-          <x14:colorHigh theme="5"/>
-          <x14:colorLow theme="5"/>
+          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
+          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
+          <x14:colorLast theme="4" tint="0.39997558519241921"/>
+          <x14:colorHigh theme="4"/>
+          <x14:colorLow theme="4"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>Sheet1!C40:N40</xm:f>
-              <xm:sqref>R40</xm:sqref>
+              <xm:f>Sheet1!C12:N12</xm:f>
+              <xm:sqref>R12</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C41:N41</xm:f>
-              <xm:sqref>R41</xm:sqref>
+              <xm:f>Sheet1!C13:N13</xm:f>
+              <xm:sqref>R13</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C42:N42</xm:f>
-              <xm:sqref>R42</xm:sqref>
+              <xm:f>Sheet1!C14:N14</xm:f>
+              <xm:sqref>R14</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C43:N43</xm:f>
-              <xm:sqref>R43</xm:sqref>
+              <xm:f>Sheet1!C15:N15</xm:f>
+              <xm:sqref>R15</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C44:N44</xm:f>
-              <xm:sqref>R44</xm:sqref>
+              <xm:f>Sheet1!C16:N16</xm:f>
+              <xm:sqref>R16</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!C17:N17</xm:f>
+              <xm:sqref>R17</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!C18:N18</xm:f>
+              <xm:sqref>R18</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!C19:N19</xm:f>
+              <xm:sqref>R19</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!C20:N20</xm:f>
+              <xm:sqref>R20</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1" xr2:uid="{91D187D6-5323-544B-B7BE-ABB6200C5BA5}">
+          <x14:colorSeries theme="4" tint="-0.499984740745262"/>
+          <x14:colorNegative theme="5"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
+          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
+          <x14:colorLast theme="4" tint="0.39997558519241921"/>
+          <x14:colorHigh theme="4"/>
+          <x14:colorLow theme="4"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Sheet1!C33:N33</xm:f>
+              <xm:sqref>R33</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1" xr2:uid="{E5835441-2CEF-4A46-B3DA-A71702CCB74C}">
+          <x14:colorSeries theme="4" tint="-0.499984740745262"/>
+          <x14:colorNegative theme="5"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
+          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
+          <x14:colorLast theme="4" tint="0.39997558519241921"/>
+          <x14:colorHigh theme="4"/>
+          <x14:colorLow theme="4"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Sheet1!C36:N36</xm:f>
+              <xm:sqref>R36</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!C37:N37</xm:f>
+              <xm:sqref>R37</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
@@ -9948,7 +10012,39 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1" xr2:uid="{E5835441-2CEF-4A46-B3DA-A71702CCB74C}">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" markers="1" high="1" low="1" xr2:uid="{3489094E-86F0-554F-8EA5-9E9DAEA9CAA8}">
+          <x14:colorSeries theme="0"/>
+          <x14:colorNegative theme="6"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers theme="0"/>
+          <x14:colorFirst theme="5" tint="0.39997558519241921"/>
+          <x14:colorLast theme="5" tint="0.39997558519241921"/>
+          <x14:colorHigh theme="5"/>
+          <x14:colorLow theme="5"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Sheet1!C40:N40</xm:f>
+              <xm:sqref>R40</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!C41:N41</xm:f>
+              <xm:sqref>R41</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!C42:N42</xm:f>
+              <xm:sqref>R42</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!C43:N43</xm:f>
+              <xm:sqref>R43</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!C44:N44</xm:f>
+              <xm:sqref>R44</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1" xr2:uid="{684D059B-A148-7B4D-9E6A-6A758AEBB88C}">
           <x14:colorSeries theme="4" tint="-0.499984740745262"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -9959,104 +10055,8 @@
           <x14:colorLow theme="4"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>Sheet1!C36:N36</xm:f>
-              <xm:sqref>R36</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>Sheet1!C37:N37</xm:f>
-              <xm:sqref>R37</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1" xr2:uid="{91D187D6-5323-544B-B7BE-ABB6200C5BA5}">
-          <x14:colorSeries theme="4" tint="-0.499984740745262"/>
-          <x14:colorNegative theme="5"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
-          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
-          <x14:colorLast theme="4" tint="0.39997558519241921"/>
-          <x14:colorHigh theme="4"/>
-          <x14:colorLow theme="4"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>Sheet1!C33:N33</xm:f>
-              <xm:sqref>R33</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1" xr2:uid="{382C768D-DF9D-8946-BAD3-24209AB66791}">
-          <x14:colorSeries theme="4" tint="-0.499984740745262"/>
-          <x14:colorNegative theme="5"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
-          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
-          <x14:colorLast theme="4" tint="0.39997558519241921"/>
-          <x14:colorHigh theme="4"/>
-          <x14:colorLow theme="4"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>Sheet1!C12:N12</xm:f>
-              <xm:sqref>R12</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>Sheet1!C13:N13</xm:f>
-              <xm:sqref>R13</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>Sheet1!C14:N14</xm:f>
-              <xm:sqref>R14</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>Sheet1!C15:N15</xm:f>
-              <xm:sqref>R15</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>Sheet1!C16:N16</xm:f>
-              <xm:sqref>R16</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>Sheet1!C17:N17</xm:f>
-              <xm:sqref>R17</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>Sheet1!C18:N18</xm:f>
-              <xm:sqref>R18</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>Sheet1!C19:N19</xm:f>
-              <xm:sqref>R19</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>Sheet1!C20:N20</xm:f>
-              <xm:sqref>R20</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1" xr2:uid="{A51D215C-6A0C-D443-9A45-6910023EF5F6}">
-          <x14:colorSeries theme="4" tint="-0.499984740745262"/>
-          <x14:colorNegative theme="5"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
-          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
-          <x14:colorLast theme="4" tint="0.39997558519241921"/>
-          <x14:colorHigh theme="4"/>
-          <x14:colorLow theme="4"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>Sheet1!C6:N6</xm:f>
-              <xm:sqref>R6</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>Sheet1!C7:N7</xm:f>
-              <xm:sqref>R7</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>Sheet1!C8:N8</xm:f>
-              <xm:sqref>R8</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>Sheet1!C9:N9</xm:f>
-              <xm:sqref>R9</xm:sqref>
+              <xm:f>Sheet1!C21:N21</xm:f>
+              <xm:sqref>R21</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
@@ -10067,6 +10067,35 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="28" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="60f5a4f2d2b0abadcf532d48ebf9cb71">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7dd78129e6a1811f84807ad11c651531" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -10378,36 +10407,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC9016F9-7015-43E2-8C51-8C9B031A2916}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61C4CF09-E16C-491E-896B-59FA5BAACD58}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5AF2BFB-A3F6-42EF-82A3-18ADC5F181D5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10428,26 +10448,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61C4CF09-E16C-491E-896B-59FA5BAACD58}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC9016F9-7015-43E2-8C51-8C9B031A2916}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata"/>
 </file>
--- a/assets/budget-template.xlsx
+++ b/assets/budget-template.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/taulo/GolandProjects/budgetpipe/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3FE1EA2-98D3-2B4D-ACC8-8BFC8362D54B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FF5C8CC-9162-274E-B6A1-0C087F0B0C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="2026" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="LastCol">COUNTA(#REF!)+1</definedName>
@@ -438,7 +438,7 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -553,6 +553,9 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="44" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="20% - Accent2" xfId="8" builtinId="34"/>
@@ -589,6 +592,619 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF7F7F7"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF7F7F7"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF7F7F7"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF7F7F7"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF7F7F7"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF7F7F7"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF7F7F7"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF7F7F7"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF7F7F7"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF7F7F7"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF7F7F7"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF7F7F7"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF7F7F7"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF7F7F7"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF7F7F7"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF7F7F7"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF7F7F7"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.14993743705557422"/>
+        <name val="verdana"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2707,619 +3323,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF7F7F7"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF7F7F7"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF7F7F7"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF7F7F7"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF7F7F7"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF7F7F7"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF7F7F7"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF7F7F7"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF7F7F7"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF7F7F7"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF7F7F7"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF7F7F7"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF7F7F7"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF7F7F7"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF7F7F7"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF7F7F7"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF7F7F7"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.14993743705557422"/>
-        <name val="verdana"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -3848,29 +3851,29 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D01C33AF-B39E-7346-82C8-45610BC0ACDD}" name="tblIncome" displayName="tblIncome" ref="B5:R9" totalsRowCount="1" headerRowDxfId="165" dataDxfId="164" totalsRowDxfId="163">
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{E570BA2C-7D65-CF4F-AFB0-0208DC5794C9}" name="INCOME" totalsRowLabel="Total" dataDxfId="162" totalsRowDxfId="161"/>
-    <tableColumn id="2" xr3:uid="{BF162114-DA3D-4F41-BF11-540DD3FF7370}" name="JAN" totalsRowFunction="sum" dataDxfId="160" totalsRowDxfId="159" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
-    <tableColumn id="3" xr3:uid="{48D8FC93-E610-0940-A046-6BE73F956999}" name="FEB" totalsRowFunction="sum" dataDxfId="158" totalsRowDxfId="157" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
-    <tableColumn id="4" xr3:uid="{CB4ED660-D615-CB45-9AE8-4E35E3B25267}" name="MAR" totalsRowFunction="sum" dataDxfId="156" totalsRowDxfId="155" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
-    <tableColumn id="5" xr3:uid="{2C7038F5-003B-944A-93AE-5A5DDC7A88E6}" name="APR" totalsRowFunction="sum" dataDxfId="154" totalsRowDxfId="153" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
-    <tableColumn id="6" xr3:uid="{19AF71B3-9524-054C-B559-E025CC844888}" name="MAY" totalsRowFunction="sum" dataDxfId="152" totalsRowDxfId="151" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
-    <tableColumn id="7" xr3:uid="{47A8FD50-30FF-A24A-B0A1-A2CD947EDC57}" name="JUN" totalsRowFunction="sum" dataDxfId="150" totalsRowDxfId="149" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
-    <tableColumn id="8" xr3:uid="{E3473B94-303D-F84B-BB99-742CF24969E9}" name="JUL" totalsRowFunction="sum" dataDxfId="148" totalsRowDxfId="147" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
-    <tableColumn id="9" xr3:uid="{5AE9406F-80F6-C547-903E-42F551EA45B8}" name="AUG" totalsRowFunction="sum" dataDxfId="146" totalsRowDxfId="145" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
-    <tableColumn id="10" xr3:uid="{0AC6E44E-37E7-FE4A-9233-FCEC98F84E12}" name="SEP" totalsRowFunction="sum" dataDxfId="144" totalsRowDxfId="143" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
-    <tableColumn id="11" xr3:uid="{115A7209-5306-854C-A9A5-2ABF4F9A4822}" name="OCT" totalsRowFunction="sum" dataDxfId="142" totalsRowDxfId="141" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
-    <tableColumn id="12" xr3:uid="{617B479F-E8D5-CE4D-A6EB-11AB8DE52EA3}" name="NOV" totalsRowFunction="sum" dataDxfId="140" totalsRowDxfId="139" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
-    <tableColumn id="13" xr3:uid="{13A7594F-70B5-894C-B4EC-B5696AC00837}" name="DEC" totalsRowFunction="sum" dataDxfId="138" totalsRowDxfId="137" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
-    <tableColumn id="14" xr3:uid="{18BA2D4B-ADA7-8548-8162-803836A47823}" name="TOTAL" totalsRowFunction="sum" dataDxfId="136" totalsRowDxfId="135" dataCellStyle="Currency" totalsRowCellStyle="Currency">
+    <tableColumn id="1" xr3:uid="{E570BA2C-7D65-CF4F-AFB0-0208DC5794C9}" name="INCOME" totalsRowLabel="Total" dataDxfId="33" totalsRowDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{BF162114-DA3D-4F41-BF11-540DD3FF7370}" name="JAN" totalsRowFunction="sum" dataDxfId="32" totalsRowDxfId="15" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
+    <tableColumn id="3" xr3:uid="{48D8FC93-E610-0940-A046-6BE73F956999}" name="FEB" totalsRowFunction="sum" dataDxfId="31" totalsRowDxfId="14" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
+    <tableColumn id="4" xr3:uid="{CB4ED660-D615-CB45-9AE8-4E35E3B25267}" name="MAR" totalsRowFunction="sum" dataDxfId="30" totalsRowDxfId="13" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
+    <tableColumn id="5" xr3:uid="{2C7038F5-003B-944A-93AE-5A5DDC7A88E6}" name="APR" totalsRowFunction="sum" dataDxfId="29" totalsRowDxfId="12" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
+    <tableColumn id="6" xr3:uid="{19AF71B3-9524-054C-B559-E025CC844888}" name="MAY" totalsRowFunction="sum" dataDxfId="28" totalsRowDxfId="11" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
+    <tableColumn id="7" xr3:uid="{47A8FD50-30FF-A24A-B0A1-A2CD947EDC57}" name="JUN" totalsRowFunction="sum" dataDxfId="27" totalsRowDxfId="10" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
+    <tableColumn id="8" xr3:uid="{E3473B94-303D-F84B-BB99-742CF24969E9}" name="JUL" totalsRowFunction="sum" dataDxfId="26" totalsRowDxfId="9" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
+    <tableColumn id="9" xr3:uid="{5AE9406F-80F6-C547-903E-42F551EA45B8}" name="AUG" totalsRowFunction="sum" dataDxfId="25" totalsRowDxfId="8" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
+    <tableColumn id="10" xr3:uid="{0AC6E44E-37E7-FE4A-9233-FCEC98F84E12}" name="SEP" totalsRowFunction="sum" dataDxfId="24" totalsRowDxfId="7" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
+    <tableColumn id="11" xr3:uid="{115A7209-5306-854C-A9A5-2ABF4F9A4822}" name="OCT" totalsRowFunction="sum" dataDxfId="23" totalsRowDxfId="6" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
+    <tableColumn id="12" xr3:uid="{617B479F-E8D5-CE4D-A6EB-11AB8DE52EA3}" name="NOV" totalsRowFunction="sum" dataDxfId="22" totalsRowDxfId="5" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
+    <tableColumn id="13" xr3:uid="{13A7594F-70B5-894C-B4EC-B5696AC00837}" name="DEC" totalsRowFunction="sum" dataDxfId="21" totalsRowDxfId="4" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
+    <tableColumn id="14" xr3:uid="{18BA2D4B-ADA7-8548-8162-803836A47823}" name="TOTAL" totalsRowFunction="sum" dataDxfId="20" totalsRowDxfId="3" dataCellStyle="Currency" totalsRowCellStyle="Currency">
       <calculatedColumnFormula>SUM(tblIncome[[#This Row],[JAN]:[DEC]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{C5410515-385A-7D4F-A9CB-44AF95BB9E1E}" name="AVG" totalsRowFunction="sum" dataDxfId="134" totalsRowDxfId="133" dataCellStyle="Currency" totalsRowCellStyle="Currency">
+    <tableColumn id="17" xr3:uid="{C5410515-385A-7D4F-A9CB-44AF95BB9E1E}" name="AVG" totalsRowFunction="sum" dataDxfId="19" totalsRowDxfId="2" dataCellStyle="Currency" totalsRowCellStyle="Currency">
       <calculatedColumnFormula>AVERAGEIF(tblIncome[[#This Row],[JAN]:[DEC]],"&gt;=0")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{259CA5E2-8B26-8F41-89B5-0CFD34C5864A}" name="MED" totalsRowFunction="sum" dataDxfId="132" totalsRowDxfId="131" dataCellStyle="Currency" totalsRowCellStyle="Currency">
+    <tableColumn id="16" xr3:uid="{259CA5E2-8B26-8F41-89B5-0CFD34C5864A}" name="MED" totalsRowFunction="sum" dataDxfId="18" totalsRowDxfId="1" dataCellStyle="Currency" totalsRowCellStyle="Currency">
       <calculatedColumnFormula>MEDIAN(tblIncome[[#This Row],[JAN]:[DEC]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{4E49A019-475D-D141-9175-12A1ABA0CF53}" name="SPARKLINE" dataDxfId="130" totalsRowDxfId="129"/>
+    <tableColumn id="15" xr3:uid="{4E49A019-475D-D141-9175-12A1ABA0CF53}" name="SPARKLINE" dataDxfId="17" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Table Style 1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="1"/>
   <extLst>
@@ -3882,31 +3885,31 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{66404086-D07C-FE4E-83EA-A9FDEAB39396}" name="tblFixed" displayName="tblFixed" ref="B11:R21" totalsRowCount="1" headerRowDxfId="128" dataDxfId="127" totalsRowDxfId="126">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{66404086-D07C-FE4E-83EA-A9FDEAB39396}" name="tblFixed" displayName="tblFixed" ref="B11:R21" totalsRowCount="1" headerRowDxfId="162" dataDxfId="161" totalsRowDxfId="160">
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{7218B040-B89C-704E-89B6-F95A0FB36621}" name="FIXED" totalsRowLabel="Total" dataDxfId="125" totalsRowDxfId="124"/>
-    <tableColumn id="2" xr3:uid="{B792F60A-FDCF-674D-AF06-1A5C81AFC928}" name="JAN" totalsRowFunction="sum" dataDxfId="123" totalsRowDxfId="122" dataCellStyle="Currency"/>
-    <tableColumn id="3" xr3:uid="{C3483CFC-04D9-B84E-AD02-8D75D7AD2364}" name="FEB" totalsRowFunction="sum" dataDxfId="121" totalsRowDxfId="120" dataCellStyle="Currency"/>
-    <tableColumn id="4" xr3:uid="{0C3DE67F-5EE2-F940-A4E8-97399F70C4E5}" name="MAR" totalsRowFunction="sum" dataDxfId="119" totalsRowDxfId="118" dataCellStyle="Currency"/>
-    <tableColumn id="5" xr3:uid="{2FC596AF-AFC3-904A-9AE1-B2BE0598ECD9}" name="APR" totalsRowFunction="sum" dataDxfId="117" totalsRowDxfId="116" dataCellStyle="Currency"/>
-    <tableColumn id="6" xr3:uid="{BEFFCB15-F6CF-6A46-AB60-2B715E9B662D}" name="MAY" totalsRowFunction="sum" dataDxfId="115" totalsRowDxfId="114" dataCellStyle="Currency"/>
-    <tableColumn id="7" xr3:uid="{E06EAE62-E7AB-1B4A-94D8-EC8D268D1FAA}" name="JUN" totalsRowFunction="sum" dataDxfId="113" totalsRowDxfId="112" dataCellStyle="Currency"/>
-    <tableColumn id="8" xr3:uid="{7483A27D-6A25-3B4C-9616-24C8407AB15E}" name="JUL" totalsRowFunction="sum" dataDxfId="111" totalsRowDxfId="110" dataCellStyle="Currency"/>
-    <tableColumn id="9" xr3:uid="{17344A7B-38BE-6C48-8FD0-60731F672BF5}" name="AUG" totalsRowFunction="sum" dataDxfId="109" totalsRowDxfId="108" dataCellStyle="Currency"/>
-    <tableColumn id="10" xr3:uid="{61CD3D14-C0C8-0049-BEE4-850E4550453C}" name="SEP" totalsRowFunction="sum" dataDxfId="107" totalsRowDxfId="106" dataCellStyle="Currency"/>
-    <tableColumn id="11" xr3:uid="{DA8ECB24-36AF-4A4A-ABB2-FAD060F5506A}" name="OCT" totalsRowFunction="sum" dataDxfId="105" totalsRowDxfId="104" dataCellStyle="Currency"/>
-    <tableColumn id="12" xr3:uid="{07934322-743A-434A-AAE2-86BF3E6FB493}" name="NOV" totalsRowFunction="sum" dataDxfId="103" totalsRowDxfId="102" dataCellStyle="Currency"/>
-    <tableColumn id="13" xr3:uid="{1FFBBD23-0890-344B-8381-0DD3B4758F0B}" name="DEC" totalsRowFunction="sum" dataDxfId="101" totalsRowDxfId="100" dataCellStyle="Currency"/>
-    <tableColumn id="14" xr3:uid="{50A875B2-5D80-5641-AECD-98B17E0DC063}" name="TOTAL" totalsRowFunction="sum" dataDxfId="99" totalsRowDxfId="98" dataCellStyle="Currency">
+    <tableColumn id="1" xr3:uid="{7218B040-B89C-704E-89B6-F95A0FB36621}" name="FIXED" totalsRowLabel="Total" dataDxfId="159" totalsRowDxfId="158"/>
+    <tableColumn id="2" xr3:uid="{B792F60A-FDCF-674D-AF06-1A5C81AFC928}" name="JAN" totalsRowFunction="sum" dataDxfId="157" totalsRowDxfId="156" dataCellStyle="Currency"/>
+    <tableColumn id="3" xr3:uid="{C3483CFC-04D9-B84E-AD02-8D75D7AD2364}" name="FEB" totalsRowFunction="sum" dataDxfId="155" totalsRowDxfId="154" dataCellStyle="Currency"/>
+    <tableColumn id="4" xr3:uid="{0C3DE67F-5EE2-F940-A4E8-97399F70C4E5}" name="MAR" totalsRowFunction="sum" dataDxfId="153" totalsRowDxfId="152" dataCellStyle="Currency"/>
+    <tableColumn id="5" xr3:uid="{2FC596AF-AFC3-904A-9AE1-B2BE0598ECD9}" name="APR" totalsRowFunction="sum" dataDxfId="151" totalsRowDxfId="150" dataCellStyle="Currency"/>
+    <tableColumn id="6" xr3:uid="{BEFFCB15-F6CF-6A46-AB60-2B715E9B662D}" name="MAY" totalsRowFunction="sum" dataDxfId="149" totalsRowDxfId="148" dataCellStyle="Currency"/>
+    <tableColumn id="7" xr3:uid="{E06EAE62-E7AB-1B4A-94D8-EC8D268D1FAA}" name="JUN" totalsRowFunction="sum" dataDxfId="147" totalsRowDxfId="146" dataCellStyle="Currency"/>
+    <tableColumn id="8" xr3:uid="{7483A27D-6A25-3B4C-9616-24C8407AB15E}" name="JUL" totalsRowFunction="sum" dataDxfId="145" totalsRowDxfId="144" dataCellStyle="Currency"/>
+    <tableColumn id="9" xr3:uid="{17344A7B-38BE-6C48-8FD0-60731F672BF5}" name="AUG" totalsRowFunction="sum" dataDxfId="143" totalsRowDxfId="142" dataCellStyle="Currency"/>
+    <tableColumn id="10" xr3:uid="{61CD3D14-C0C8-0049-BEE4-850E4550453C}" name="SEP" totalsRowFunction="sum" dataDxfId="141" totalsRowDxfId="140" dataCellStyle="Currency"/>
+    <tableColumn id="11" xr3:uid="{DA8ECB24-36AF-4A4A-ABB2-FAD060F5506A}" name="OCT" totalsRowFunction="sum" dataDxfId="139" totalsRowDxfId="138" dataCellStyle="Currency"/>
+    <tableColumn id="12" xr3:uid="{07934322-743A-434A-AAE2-86BF3E6FB493}" name="NOV" totalsRowFunction="sum" dataDxfId="137" totalsRowDxfId="136" dataCellStyle="Currency"/>
+    <tableColumn id="13" xr3:uid="{1FFBBD23-0890-344B-8381-0DD3B4758F0B}" name="DEC" totalsRowFunction="sum" dataDxfId="135" totalsRowDxfId="134" dataCellStyle="Currency"/>
+    <tableColumn id="14" xr3:uid="{50A875B2-5D80-5641-AECD-98B17E0DC063}" name="TOTAL" totalsRowFunction="sum" dataDxfId="133" totalsRowDxfId="132" dataCellStyle="Currency">
       <calculatedColumnFormula>SUM(tblFixed[[#This Row],[JAN]:[DEC]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{CE93D4EA-4453-7C45-A70C-233430B9452C}" name="AVG" totalsRowFunction="sum" dataDxfId="97" totalsRowDxfId="96" dataCellStyle="Currency">
+    <tableColumn id="15" xr3:uid="{CE93D4EA-4453-7C45-A70C-233430B9452C}" name="AVG" totalsRowFunction="sum" dataDxfId="131" totalsRowDxfId="130" dataCellStyle="Currency">
       <calculatedColumnFormula>AVERAGEIF(tblFixed[[#This Row],[JAN]:[DEC]],"&lt;=0")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{CC87E450-EFFE-9A47-8058-E1413EC2CA14}" name="MED" totalsRowFunction="sum" dataDxfId="95" totalsRowDxfId="94" dataCellStyle="Currency">
+    <tableColumn id="16" xr3:uid="{CC87E450-EFFE-9A47-8058-E1413EC2CA14}" name="MED" totalsRowFunction="sum" dataDxfId="129" totalsRowDxfId="128" dataCellStyle="Currency">
       <calculatedColumnFormula>MEDIAN(tblFixed[[#This Row],[JAN]:[DEC]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{2FF721F3-FC7D-E34A-A6AA-092EA0B357BE}" name="SPARKLINE" dataDxfId="93" totalsRowDxfId="92" dataCellStyle="Currency"/>
+    <tableColumn id="17" xr3:uid="{2FF721F3-FC7D-E34A-A6AA-092EA0B357BE}" name="SPARKLINE" dataDxfId="127" totalsRowDxfId="126" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="Table Style 1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="1"/>
   <extLst>
@@ -3918,31 +3921,31 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{6569D38E-6245-AE4B-A792-59BF998FDE54}" name="tblVariable" displayName="tblVariable" ref="B22:R33" totalsRowCount="1" headerRowDxfId="91" dataDxfId="90" totalsRowDxfId="89">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{6569D38E-6245-AE4B-A792-59BF998FDE54}" name="tblVariable" displayName="tblVariable" ref="B22:R33" totalsRowCount="1" headerRowDxfId="125" dataDxfId="124" totalsRowDxfId="123">
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{2DFD2C0E-6649-0444-8936-6E4F63A7A5A6}" name="VARIABLE" totalsRowLabel="Total" dataDxfId="88" totalsRowDxfId="87"/>
-    <tableColumn id="2" xr3:uid="{C7391998-5A09-F747-9D32-1884CA05F01B}" name="JAN" totalsRowFunction="sum" dataDxfId="86" totalsRowDxfId="85" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
-    <tableColumn id="3" xr3:uid="{79F17425-6FD5-814B-92D2-04C05281AF39}" name="FEB" totalsRowFunction="sum" dataDxfId="84" totalsRowDxfId="83" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
-    <tableColumn id="4" xr3:uid="{C6ED7F46-941D-3A43-A78F-227BFAF4F9FC}" name="MAR" totalsRowFunction="sum" dataDxfId="82" totalsRowDxfId="81" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
-    <tableColumn id="5" xr3:uid="{61751259-B7E1-FC44-A3CE-F676FBA69A9C}" name="APR" totalsRowFunction="sum" dataDxfId="80" totalsRowDxfId="79" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
-    <tableColumn id="6" xr3:uid="{C91CBF3F-51E4-9D4A-969B-B4985FBFA8C9}" name="MAY" totalsRowFunction="sum" dataDxfId="78" totalsRowDxfId="77" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
-    <tableColumn id="7" xr3:uid="{E5282557-60B1-8F4A-89E0-DC7406A3FA82}" name="JUN" totalsRowFunction="sum" dataDxfId="76" totalsRowDxfId="75" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
-    <tableColumn id="8" xr3:uid="{AE9104A3-EAEF-6741-A18F-B09EFB42C874}" name="JUL" totalsRowFunction="sum" dataDxfId="74" totalsRowDxfId="73" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
-    <tableColumn id="9" xr3:uid="{EC4D0BF6-4FAE-7F4E-8EBB-D2CD0E28DCB5}" name="AUG" totalsRowFunction="sum" dataDxfId="72" totalsRowDxfId="71" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
-    <tableColumn id="10" xr3:uid="{6DC91D8C-337D-5D49-9E2D-94C5D7267C7E}" name="SEP" totalsRowFunction="sum" dataDxfId="70" totalsRowDxfId="69" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
-    <tableColumn id="11" xr3:uid="{A251B7EE-376C-5F43-A457-9261CE506F3D}" name="OCT" totalsRowFunction="sum" dataDxfId="68" totalsRowDxfId="67" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
-    <tableColumn id="12" xr3:uid="{F5CBFD5A-01B2-A543-B75C-F9CF31C043F8}" name="NOV" totalsRowFunction="sum" dataDxfId="66" totalsRowDxfId="65" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
-    <tableColumn id="13" xr3:uid="{FD758FA9-E23C-ED4A-B63D-54AE803A68C7}" name="DEC" totalsRowFunction="sum" dataDxfId="64" totalsRowDxfId="63" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
-    <tableColumn id="14" xr3:uid="{A640743B-4AC6-E44B-B519-E4E20EDFD578}" name="TOTAL" totalsRowFunction="sum" dataDxfId="62" totalsRowDxfId="61" dataCellStyle="Currency" totalsRowCellStyle="Currency">
+    <tableColumn id="1" xr3:uid="{2DFD2C0E-6649-0444-8936-6E4F63A7A5A6}" name="VARIABLE" totalsRowLabel="Total" dataDxfId="122" totalsRowDxfId="121"/>
+    <tableColumn id="2" xr3:uid="{C7391998-5A09-F747-9D32-1884CA05F01B}" name="JAN" totalsRowFunction="sum" dataDxfId="120" totalsRowDxfId="119" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
+    <tableColumn id="3" xr3:uid="{79F17425-6FD5-814B-92D2-04C05281AF39}" name="FEB" totalsRowFunction="sum" dataDxfId="118" totalsRowDxfId="117" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
+    <tableColumn id="4" xr3:uid="{C6ED7F46-941D-3A43-A78F-227BFAF4F9FC}" name="MAR" totalsRowFunction="sum" dataDxfId="116" totalsRowDxfId="115" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
+    <tableColumn id="5" xr3:uid="{61751259-B7E1-FC44-A3CE-F676FBA69A9C}" name="APR" totalsRowFunction="sum" dataDxfId="114" totalsRowDxfId="113" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
+    <tableColumn id="6" xr3:uid="{C91CBF3F-51E4-9D4A-969B-B4985FBFA8C9}" name="MAY" totalsRowFunction="sum" dataDxfId="112" totalsRowDxfId="111" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
+    <tableColumn id="7" xr3:uid="{E5282557-60B1-8F4A-89E0-DC7406A3FA82}" name="JUN" totalsRowFunction="sum" dataDxfId="110" totalsRowDxfId="109" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
+    <tableColumn id="8" xr3:uid="{AE9104A3-EAEF-6741-A18F-B09EFB42C874}" name="JUL" totalsRowFunction="sum" dataDxfId="108" totalsRowDxfId="107" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
+    <tableColumn id="9" xr3:uid="{EC4D0BF6-4FAE-7F4E-8EBB-D2CD0E28DCB5}" name="AUG" totalsRowFunction="sum" dataDxfId="106" totalsRowDxfId="105" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
+    <tableColumn id="10" xr3:uid="{6DC91D8C-337D-5D49-9E2D-94C5D7267C7E}" name="SEP" totalsRowFunction="sum" dataDxfId="104" totalsRowDxfId="103" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
+    <tableColumn id="11" xr3:uid="{A251B7EE-376C-5F43-A457-9261CE506F3D}" name="OCT" totalsRowFunction="sum" dataDxfId="102" totalsRowDxfId="101" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
+    <tableColumn id="12" xr3:uid="{F5CBFD5A-01B2-A543-B75C-F9CF31C043F8}" name="NOV" totalsRowFunction="sum" dataDxfId="100" totalsRowDxfId="99" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
+    <tableColumn id="13" xr3:uid="{FD758FA9-E23C-ED4A-B63D-54AE803A68C7}" name="DEC" totalsRowFunction="sum" dataDxfId="98" totalsRowDxfId="97" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
+    <tableColumn id="14" xr3:uid="{A640743B-4AC6-E44B-B519-E4E20EDFD578}" name="TOTAL" totalsRowFunction="sum" dataDxfId="96" totalsRowDxfId="95" dataCellStyle="Currency" totalsRowCellStyle="Currency">
       <calculatedColumnFormula>SUM(tblVariable[[#This Row],[JAN]:[DEC]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{CAF20004-DD01-2845-A797-9EB80A1CA007}" name="AVG" totalsRowFunction="sum" dataDxfId="60" totalsRowDxfId="59" dataCellStyle="Currency" totalsRowCellStyle="Currency">
+    <tableColumn id="15" xr3:uid="{CAF20004-DD01-2845-A797-9EB80A1CA007}" name="AVG" totalsRowFunction="sum" dataDxfId="94" totalsRowDxfId="93" dataCellStyle="Currency" totalsRowCellStyle="Currency">
       <calculatedColumnFormula>AVERAGEIF(tblVariable[[#This Row],[JAN]:[DEC]],"&lt;=0")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{F510BBB5-5E81-6D49-B4F6-7B828907F237}" name="MED" totalsRowFunction="sum" dataDxfId="58" totalsRowDxfId="57" dataCellStyle="Currency" totalsRowCellStyle="Currency">
+    <tableColumn id="17" xr3:uid="{F510BBB5-5E81-6D49-B4F6-7B828907F237}" name="MED" totalsRowFunction="sum" dataDxfId="92" totalsRowDxfId="91" dataCellStyle="Currency" totalsRowCellStyle="Currency">
       <calculatedColumnFormula>MEDIAN(tblVariable[[#This Row],[JAN]:[DEC]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{5D351838-4696-3B44-8E25-A2783BDE825F}" name="SPARKLINE" dataDxfId="56" totalsRowDxfId="55" dataCellStyle="Currency"/>
+    <tableColumn id="18" xr3:uid="{5D351838-4696-3B44-8E25-A2783BDE825F}" name="SPARKLINE" dataDxfId="90" totalsRowDxfId="89" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="Table Style 1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="1"/>
   <extLst>
@@ -3954,25 +3957,25 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{B54D96C8-B74E-2946-B4C2-8B65E37B1DEF}" name="tblTotals" displayName="tblTotals" ref="B39:R44" totalsRowShown="0" dataDxfId="54" headerRowCellStyle="Accent1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{B54D96C8-B74E-2946-B4C2-8B65E37B1DEF}" name="tblTotals" displayName="tblTotals" ref="B39:R44" totalsRowShown="0" dataDxfId="88" headerRowCellStyle="Accent1">
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{AEB778AB-6508-6F41-B6C8-9970D4E1F6BA}" name="TOTALS" dataDxfId="53" dataCellStyle="Accent4"/>
-    <tableColumn id="2" xr3:uid="{ECBCEAF6-76F1-8C49-8B6D-BC553DC21645}" name="JAN" dataDxfId="52" dataCellStyle="Accent1"/>
-    <tableColumn id="3" xr3:uid="{79067FA4-519D-0C49-9E35-9B219A5031CF}" name="FEB" dataDxfId="51" dataCellStyle="Accent4"/>
-    <tableColumn id="4" xr3:uid="{4D4A12DB-9B30-9B44-84BE-782E42EC825A}" name="MAR" dataDxfId="50" dataCellStyle="Accent1"/>
-    <tableColumn id="5" xr3:uid="{C08E6452-7F23-664F-94BF-DDD9A32BF875}" name="APR" dataDxfId="49" dataCellStyle="Accent4"/>
-    <tableColumn id="6" xr3:uid="{5349CE7F-D71E-094E-BF5E-C0C2E430AA78}" name="MAY" dataDxfId="48" dataCellStyle="Accent1"/>
-    <tableColumn id="7" xr3:uid="{4533C7EC-E932-AB4E-AEFF-73C8B0AFF45E}" name="JUN" dataDxfId="47" dataCellStyle="Accent4"/>
-    <tableColumn id="8" xr3:uid="{0B56A8BA-B041-D645-BDA5-905A780D465F}" name="JUL" dataDxfId="46" dataCellStyle="Currency"/>
-    <tableColumn id="9" xr3:uid="{B6FE280A-CA81-9D4E-B9FE-ECE79858961B}" name="AUG" dataDxfId="45" dataCellStyle="Accent4"/>
-    <tableColumn id="10" xr3:uid="{83009CEE-F18F-BB47-8E88-69730037765C}" name="SEP" dataDxfId="44" dataCellStyle="Currency"/>
-    <tableColumn id="11" xr3:uid="{BBC825C3-C5D8-D346-BF3B-7FCA2801F67A}" name="OCT" dataDxfId="43" dataCellStyle="Accent4"/>
-    <tableColumn id="12" xr3:uid="{47E0A368-3F1E-9F4E-838A-E3AFC338BC8F}" name="NOV" dataDxfId="42" dataCellStyle="Currency"/>
-    <tableColumn id="13" xr3:uid="{E4F0C5A6-CED5-824A-8781-496F8CD1FC39}" name="DEC" dataDxfId="41" dataCellStyle="Accent4"/>
-    <tableColumn id="14" xr3:uid="{4D568E1F-E1F5-0C45-9E58-5513807BB8DA}" name="TOTAL" dataDxfId="40" dataCellStyle="Currency"/>
-    <tableColumn id="15" xr3:uid="{9358C20A-E879-1E41-845E-C7FE0904F0FA}" name="AVG" dataDxfId="39" dataCellStyle="Accent4"/>
-    <tableColumn id="16" xr3:uid="{11488D2F-F7BF-1D4D-93EC-A959FDE33094}" name="MED" dataDxfId="38" dataCellStyle="Currency"/>
-    <tableColumn id="17" xr3:uid="{7E795274-ECB2-3E49-916B-8B59D27394A0}" name="SPARKLINE" dataDxfId="37" dataCellStyle="Accent4"/>
+    <tableColumn id="1" xr3:uid="{AEB778AB-6508-6F41-B6C8-9970D4E1F6BA}" name="TOTALS" dataDxfId="87" dataCellStyle="Accent4"/>
+    <tableColumn id="2" xr3:uid="{ECBCEAF6-76F1-8C49-8B6D-BC553DC21645}" name="JAN" dataDxfId="86" dataCellStyle="Accent1"/>
+    <tableColumn id="3" xr3:uid="{79067FA4-519D-0C49-9E35-9B219A5031CF}" name="FEB" dataDxfId="85" dataCellStyle="Accent4"/>
+    <tableColumn id="4" xr3:uid="{4D4A12DB-9B30-9B44-84BE-782E42EC825A}" name="MAR" dataDxfId="84" dataCellStyle="Accent1"/>
+    <tableColumn id="5" xr3:uid="{C08E6452-7F23-664F-94BF-DDD9A32BF875}" name="APR" dataDxfId="83" dataCellStyle="Accent4"/>
+    <tableColumn id="6" xr3:uid="{5349CE7F-D71E-094E-BF5E-C0C2E430AA78}" name="MAY" dataDxfId="82" dataCellStyle="Accent1"/>
+    <tableColumn id="7" xr3:uid="{4533C7EC-E932-AB4E-AEFF-73C8B0AFF45E}" name="JUN" dataDxfId="81" dataCellStyle="Accent4"/>
+    <tableColumn id="8" xr3:uid="{0B56A8BA-B041-D645-BDA5-905A780D465F}" name="JUL" dataDxfId="80" dataCellStyle="Currency"/>
+    <tableColumn id="9" xr3:uid="{B6FE280A-CA81-9D4E-B9FE-ECE79858961B}" name="AUG" dataDxfId="79" dataCellStyle="Accent4"/>
+    <tableColumn id="10" xr3:uid="{83009CEE-F18F-BB47-8E88-69730037765C}" name="SEP" dataDxfId="78" dataCellStyle="Currency"/>
+    <tableColumn id="11" xr3:uid="{BBC825C3-C5D8-D346-BF3B-7FCA2801F67A}" name="OCT" dataDxfId="77" dataCellStyle="Accent4"/>
+    <tableColumn id="12" xr3:uid="{47E0A368-3F1E-9F4E-838A-E3AFC338BC8F}" name="NOV" dataDxfId="76" dataCellStyle="Currency"/>
+    <tableColumn id="13" xr3:uid="{E4F0C5A6-CED5-824A-8781-496F8CD1FC39}" name="DEC" dataDxfId="75" dataCellStyle="Accent4"/>
+    <tableColumn id="14" xr3:uid="{4D568E1F-E1F5-0C45-9E58-5513807BB8DA}" name="TOTAL" dataDxfId="74" dataCellStyle="Currency"/>
+    <tableColumn id="15" xr3:uid="{9358C20A-E879-1E41-845E-C7FE0904F0FA}" name="AVG" dataDxfId="73" dataCellStyle="Accent4"/>
+    <tableColumn id="16" xr3:uid="{11488D2F-F7BF-1D4D-93EC-A959FDE33094}" name="MED" dataDxfId="72" dataCellStyle="Currency"/>
+    <tableColumn id="17" xr3:uid="{7E795274-ECB2-3E49-916B-8B59D27394A0}" name="SPARKLINE" dataDxfId="71" dataCellStyle="Accent4"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="1"/>
   <extLst>
@@ -3984,31 +3987,31 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{992450C3-516C-E54A-8E9D-60C940989794}" name="tblInvestment" displayName="tblInvestment" ref="B35:R37" totalsRowCount="1" headerRowDxfId="36" dataDxfId="35" totalsRowDxfId="34">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{992450C3-516C-E54A-8E9D-60C940989794}" name="tblInvestment" displayName="tblInvestment" ref="B35:R37" totalsRowCount="1" headerRowDxfId="70" dataDxfId="69" totalsRowDxfId="68">
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{294014AF-D891-F449-B566-7F4086B30F5D}" name="INVESTMENT" totalsRowLabel="Total" dataDxfId="33" totalsRowDxfId="32"/>
-    <tableColumn id="2" xr3:uid="{15C43410-3504-934F-9BE6-940C4BC3EB1C}" name="JAN" totalsRowFunction="sum" dataDxfId="31" totalsRowDxfId="30" dataCellStyle="Currency"/>
-    <tableColumn id="3" xr3:uid="{313B1E83-6D0C-3947-AB16-91A5B56D7B46}" name="FEB" totalsRowFunction="sum" dataDxfId="29" totalsRowDxfId="28" dataCellStyle="Currency"/>
-    <tableColumn id="4" xr3:uid="{9C5E5D1F-F6CE-2143-99A3-AD994D06E5AF}" name="MAR" totalsRowFunction="sum" dataDxfId="27" totalsRowDxfId="26" dataCellStyle="Currency"/>
-    <tableColumn id="5" xr3:uid="{C3E012AE-4AAD-2146-AF94-58319121E8DD}" name="APR" totalsRowFunction="sum" dataDxfId="25" totalsRowDxfId="24" dataCellStyle="Currency"/>
-    <tableColumn id="6" xr3:uid="{577F144F-51EC-AB4B-AF91-E945C4A1B2BC}" name="MAY" totalsRowFunction="sum" dataDxfId="23" totalsRowDxfId="22" dataCellStyle="Currency"/>
-    <tableColumn id="7" xr3:uid="{DCDB89FE-34A0-4D4E-9201-C3623E2F8896}" name="JUN" totalsRowFunction="sum" dataDxfId="21" totalsRowDxfId="20" dataCellStyle="Currency"/>
-    <tableColumn id="8" xr3:uid="{2A44951E-CCCB-0447-91FA-68374BB208D0}" name="JUL" totalsRowFunction="sum" dataDxfId="19" totalsRowDxfId="18" dataCellStyle="Currency"/>
-    <tableColumn id="9" xr3:uid="{694F199B-9ABA-D54F-95D4-E62D55AE340D}" name="AUG" totalsRowFunction="sum" dataDxfId="17" totalsRowDxfId="16" dataCellStyle="Currency"/>
-    <tableColumn id="10" xr3:uid="{73668DD0-3192-F74F-A607-7282D6844B79}" name="SEP" totalsRowFunction="sum" dataDxfId="15" totalsRowDxfId="14" dataCellStyle="Currency"/>
-    <tableColumn id="11" xr3:uid="{D1F09B50-63EF-954F-A630-252B118F69BD}" name="OCT" totalsRowFunction="sum" dataDxfId="13" totalsRowDxfId="12" dataCellStyle="Currency"/>
-    <tableColumn id="12" xr3:uid="{32F0E92C-55F7-984F-9A71-48FE200865C7}" name="NOV" totalsRowFunction="sum" dataDxfId="11" totalsRowDxfId="10" dataCellStyle="Currency"/>
-    <tableColumn id="13" xr3:uid="{41E80EA4-43CB-B740-99FD-F01662477345}" name="DEC" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="8" dataCellStyle="Currency"/>
-    <tableColumn id="14" xr3:uid="{3440B9C2-E91C-414C-96C9-BDFF292029FB}" name="TOTAL" totalsRowFunction="sum" dataDxfId="7" totalsRowDxfId="6" dataCellStyle="Currency">
+    <tableColumn id="1" xr3:uid="{294014AF-D891-F449-B566-7F4086B30F5D}" name="INVESTMENT" totalsRowLabel="Total" dataDxfId="67" totalsRowDxfId="66"/>
+    <tableColumn id="2" xr3:uid="{15C43410-3504-934F-9BE6-940C4BC3EB1C}" name="JAN" totalsRowFunction="sum" dataDxfId="65" totalsRowDxfId="64" dataCellStyle="Currency"/>
+    <tableColumn id="3" xr3:uid="{313B1E83-6D0C-3947-AB16-91A5B56D7B46}" name="FEB" totalsRowFunction="sum" dataDxfId="63" totalsRowDxfId="62" dataCellStyle="Currency"/>
+    <tableColumn id="4" xr3:uid="{9C5E5D1F-F6CE-2143-99A3-AD994D06E5AF}" name="MAR" totalsRowFunction="sum" dataDxfId="61" totalsRowDxfId="60" dataCellStyle="Currency"/>
+    <tableColumn id="5" xr3:uid="{C3E012AE-4AAD-2146-AF94-58319121E8DD}" name="APR" totalsRowFunction="sum" dataDxfId="59" totalsRowDxfId="58" dataCellStyle="Currency"/>
+    <tableColumn id="6" xr3:uid="{577F144F-51EC-AB4B-AF91-E945C4A1B2BC}" name="MAY" totalsRowFunction="sum" dataDxfId="57" totalsRowDxfId="56" dataCellStyle="Currency"/>
+    <tableColumn id="7" xr3:uid="{DCDB89FE-34A0-4D4E-9201-C3623E2F8896}" name="JUN" totalsRowFunction="sum" dataDxfId="55" totalsRowDxfId="54" dataCellStyle="Currency"/>
+    <tableColumn id="8" xr3:uid="{2A44951E-CCCB-0447-91FA-68374BB208D0}" name="JUL" totalsRowFunction="sum" dataDxfId="53" totalsRowDxfId="52" dataCellStyle="Currency"/>
+    <tableColumn id="9" xr3:uid="{694F199B-9ABA-D54F-95D4-E62D55AE340D}" name="AUG" totalsRowFunction="sum" dataDxfId="51" totalsRowDxfId="50" dataCellStyle="Currency"/>
+    <tableColumn id="10" xr3:uid="{73668DD0-3192-F74F-A607-7282D6844B79}" name="SEP" totalsRowFunction="sum" dataDxfId="49" totalsRowDxfId="48" dataCellStyle="Currency"/>
+    <tableColumn id="11" xr3:uid="{D1F09B50-63EF-954F-A630-252B118F69BD}" name="OCT" totalsRowFunction="sum" dataDxfId="47" totalsRowDxfId="46" dataCellStyle="Currency"/>
+    <tableColumn id="12" xr3:uid="{32F0E92C-55F7-984F-9A71-48FE200865C7}" name="NOV" totalsRowFunction="sum" dataDxfId="45" totalsRowDxfId="44" dataCellStyle="Currency"/>
+    <tableColumn id="13" xr3:uid="{41E80EA4-43CB-B740-99FD-F01662477345}" name="DEC" totalsRowFunction="sum" dataDxfId="43" totalsRowDxfId="42" dataCellStyle="Currency"/>
+    <tableColumn id="14" xr3:uid="{3440B9C2-E91C-414C-96C9-BDFF292029FB}" name="TOTAL" totalsRowFunction="sum" dataDxfId="41" totalsRowDxfId="40" dataCellStyle="Currency">
       <calculatedColumnFormula>SUM(tblInvestment[[#This Row],[JAN]:[DEC]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{87EBC5D5-E6EE-1C40-9266-76AE68FD5A68}" name="AVG" totalsRowFunction="sum" dataDxfId="5" totalsRowDxfId="4" dataCellStyle="Currency">
+    <tableColumn id="17" xr3:uid="{87EBC5D5-E6EE-1C40-9266-76AE68FD5A68}" name="AVG" totalsRowFunction="sum" dataDxfId="39" totalsRowDxfId="38" dataCellStyle="Currency">
       <calculatedColumnFormula>AVERAGEIF(tblInvestment[[#This Row],[JAN]:[DEC]],"&gt;=0")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{19F050A6-4569-D54D-B761-D1AA987ED540}" name="MED" totalsRowFunction="sum" dataDxfId="3" totalsRowDxfId="2" dataCellStyle="Currency">
+    <tableColumn id="16" xr3:uid="{19F050A6-4569-D54D-B761-D1AA987ED540}" name="MED" totalsRowFunction="sum" dataDxfId="37" totalsRowDxfId="36" dataCellStyle="Currency">
       <calculatedColumnFormula>MEDIAN(tblInvestment[[#This Row],[JAN]:[DEC]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{898DD70E-5E50-5847-B391-F60D3CE918FB}" name="SPARKLINE" dataDxfId="1" totalsRowDxfId="0"/>
+    <tableColumn id="15" xr3:uid="{898DD70E-5E50-5847-B391-F60D3CE918FB}" name="SPARKLINE" dataDxfId="35" totalsRowDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="Table Style 1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="1"/>
   <extLst>
@@ -4586,63 +4589,63 @@
       <c r="B9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="42">
         <f>SUBTOTAL(109,tblIncome[JAN])</f>
         <v>0</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="42">
         <f>SUBTOTAL(109,tblIncome[FEB])</f>
         <v>0</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="42">
         <f>SUBTOTAL(109,tblIncome[MAR])</f>
         <v>0</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="42">
         <f>SUBTOTAL(109,tblIncome[APR])</f>
         <v>0</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="42">
         <f>SUBTOTAL(109,tblIncome[MAY])</f>
         <v>0</v>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="42">
         <f>SUBTOTAL(109,tblIncome[JUN])</f>
         <v>0</v>
       </c>
-      <c r="I9" s="22">
+      <c r="I9" s="42">
         <f>SUBTOTAL(109,tblIncome[JUL])</f>
         <v>0</v>
       </c>
-      <c r="J9" s="22">
+      <c r="J9" s="42">
         <f>SUBTOTAL(109,tblIncome[AUG])</f>
         <v>0</v>
       </c>
-      <c r="K9" s="22">
+      <c r="K9" s="42">
         <f>SUBTOTAL(109,tblIncome[SEP])</f>
         <v>0</v>
       </c>
-      <c r="L9" s="22">
+      <c r="L9" s="42">
         <f>SUBTOTAL(109,tblIncome[OCT])</f>
         <v>0</v>
       </c>
-      <c r="M9" s="22">
+      <c r="M9" s="42">
         <f>SUBTOTAL(109,tblIncome[NOV])</f>
         <v>0</v>
       </c>
-      <c r="N9" s="22">
+      <c r="N9" s="42">
         <f>SUBTOTAL(109,tblIncome[DEC])</f>
         <v>0</v>
       </c>
-      <c r="O9" s="22">
+      <c r="O9" s="42">
         <f>SUBTOTAL(109,tblIncome[TOTAL])</f>
         <v>0</v>
       </c>
-      <c r="P9" s="22" t="e">
+      <c r="P9" s="42" t="e">
         <f>SUBTOTAL(109,tblIncome[AVG])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q9" s="22" t="e">
+      <c r="Q9" s="42" t="e">
         <f>SUBTOTAL(109,tblIncome[MED])</f>
         <v>#NUM!</v>
       </c>
@@ -9848,34 +9851,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
       <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1" xr2:uid="{A51D215C-6A0C-D443-9A45-6910023EF5F6}">
-          <x14:colorSeries theme="4" tint="-0.499984740745262"/>
-          <x14:colorNegative theme="5"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
-          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
-          <x14:colorLast theme="4" tint="0.39997558519241921"/>
-          <x14:colorHigh theme="4"/>
-          <x14:colorLow theme="4"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>Sheet1!C6:N6</xm:f>
-              <xm:sqref>R6</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>Sheet1!C7:N7</xm:f>
-              <xm:sqref>R7</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>Sheet1!C8:N8</xm:f>
-              <xm:sqref>R8</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>Sheet1!C9:N9</xm:f>
-              <xm:sqref>R9</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
         <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1" xr2:uid="{382C768D-DF9D-8946-BAD3-24209AB66791}">
           <x14:colorSeries theme="4" tint="-0.499984740745262"/>
           <x14:colorNegative theme="5"/>
@@ -9887,39 +9862,39 @@
           <x14:colorLow theme="4"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>Sheet1!C12:N12</xm:f>
+              <xm:f>'2026'!C12:N12</xm:f>
               <xm:sqref>R12</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C13:N13</xm:f>
+              <xm:f>'2026'!C13:N13</xm:f>
               <xm:sqref>R13</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C14:N14</xm:f>
+              <xm:f>'2026'!C14:N14</xm:f>
               <xm:sqref>R14</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C15:N15</xm:f>
+              <xm:f>'2026'!C15:N15</xm:f>
               <xm:sqref>R15</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C16:N16</xm:f>
+              <xm:f>'2026'!C16:N16</xm:f>
               <xm:sqref>R16</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C17:N17</xm:f>
+              <xm:f>'2026'!C17:N17</xm:f>
               <xm:sqref>R17</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C18:N18</xm:f>
+              <xm:f>'2026'!C18:N18</xm:f>
               <xm:sqref>R18</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C19:N19</xm:f>
+              <xm:f>'2026'!C19:N19</xm:f>
               <xm:sqref>R19</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C20:N20</xm:f>
+              <xm:f>'2026'!C20:N20</xm:f>
               <xm:sqref>R20</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
@@ -9935,7 +9910,7 @@
           <x14:colorLow theme="4"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>Sheet1!C33:N33</xm:f>
+              <xm:f>'2026'!C33:N33</xm:f>
               <xm:sqref>R33</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
@@ -9951,11 +9926,11 @@
           <x14:colorLow theme="4"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>Sheet1!C36:N36</xm:f>
+              <xm:f>'2026'!C36:N36</xm:f>
               <xm:sqref>R36</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C37:N37</xm:f>
+              <xm:f>'2026'!C37:N37</xm:f>
               <xm:sqref>R37</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
@@ -9971,43 +9946,43 @@
           <x14:colorLow theme="4"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>Sheet1!C23:N23</xm:f>
+              <xm:f>'2026'!C23:N23</xm:f>
               <xm:sqref>R23</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C24:N24</xm:f>
+              <xm:f>'2026'!C24:N24</xm:f>
               <xm:sqref>R24</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C25:N25</xm:f>
+              <xm:f>'2026'!C25:N25</xm:f>
               <xm:sqref>R25</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C26:N26</xm:f>
+              <xm:f>'2026'!C26:N26</xm:f>
               <xm:sqref>R26</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C27:N27</xm:f>
+              <xm:f>'2026'!C27:N27</xm:f>
               <xm:sqref>R27</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C28:N28</xm:f>
+              <xm:f>'2026'!C28:N28</xm:f>
               <xm:sqref>R28</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C29:N29</xm:f>
+              <xm:f>'2026'!C29:N29</xm:f>
               <xm:sqref>R29</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C30:N30</xm:f>
+              <xm:f>'2026'!C30:N30</xm:f>
               <xm:sqref>R30</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C31:N31</xm:f>
+              <xm:f>'2026'!C31:N31</xm:f>
               <xm:sqref>R31</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C32:N32</xm:f>
+              <xm:f>'2026'!C32:N32</xm:f>
               <xm:sqref>R32</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
@@ -10023,23 +9998,23 @@
           <x14:colorLow theme="5"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>Sheet1!C40:N40</xm:f>
+              <xm:f>'2026'!C40:N40</xm:f>
               <xm:sqref>R40</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C41:N41</xm:f>
+              <xm:f>'2026'!C41:N41</xm:f>
               <xm:sqref>R41</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C42:N42</xm:f>
+              <xm:f>'2026'!C42:N42</xm:f>
               <xm:sqref>R42</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C43:N43</xm:f>
+              <xm:f>'2026'!C43:N43</xm:f>
               <xm:sqref>R43</xm:sqref>
             </x14:sparkline>
             <x14:sparkline>
-              <xm:f>Sheet1!C44:N44</xm:f>
+              <xm:f>'2026'!C44:N44</xm:f>
               <xm:sqref>R44</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
@@ -10055,8 +10030,36 @@
           <x14:colorLow theme="4"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>Sheet1!C21:N21</xm:f>
+              <xm:f>'2026'!C21:N21</xm:f>
               <xm:sqref>R21</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1" xr2:uid="{A51D215C-6A0C-D443-9A45-6910023EF5F6}">
+          <x14:colorSeries theme="4" tint="-0.499984740745262"/>
+          <x14:colorNegative theme="5"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
+          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
+          <x14:colorLast theme="4" tint="0.39997558519241921"/>
+          <x14:colorHigh theme="4"/>
+          <x14:colorLow theme="4"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'2026'!C6:N6</xm:f>
+              <xm:sqref>R6</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'2026'!C7:N7</xm:f>
+              <xm:sqref>R7</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'2026'!C8:N8</xm:f>
+              <xm:sqref>R8</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'2026'!C9:N9</xm:f>
+              <xm:sqref>R9</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
@@ -10067,6 +10070,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -10084,15 +10096,6 @@
     <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10408,6 +10411,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61C4CF09-E16C-491E-896B-59FA5BAACD58}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC9016F9-7015-43E2-8C51-8C9B031A2916}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -10415,14 +10426,6 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
     <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
     <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61C4CF09-E16C-491E-896B-59FA5BAACD58}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
